--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/reiProjects/product-automation/govgrants-product-automation/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DC659A-1C81-4201-B060-5FA51B815794}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD9C9B1-31F1-9047-ADD7-26F99A9AFCE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="5720" yWindow="7880" windowWidth="23260" windowHeight="12580" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="129">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -445,13 +445,19 @@
   </si>
   <si>
     <t>Automation Grant For PR</t>
+  </si>
+  <si>
+    <t>Basic Field Grant Office</t>
+  </si>
+  <si>
+    <t>Bankers Small Business Community Development Corporation Of California</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +475,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -487,6 +494,7 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Helvetica"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -510,6 +518,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -532,7 +546,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -554,6 +568,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -870,13 +886,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62ACE97-36F7-4E73-A259-A264DD733BB1}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -887,7 +903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -898,7 +914,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -909,7 +925,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -920,7 +936,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -940,13 +956,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A057E164-C642-4069-AA67-BFDDC1682771}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -968,7 +984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -979,7 +995,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -990,7 +1006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1001,7 +1017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1012,7 +1028,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1031,14 +1047,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69DD06D-7A8F-4C83-860C-E6A58CC62982}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1060,7 +1076,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1071,7 +1087,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1082,7 +1098,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1093,7 +1109,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1104,7 +1120,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1126,7 +1142,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1137,7 +1153,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1148,7 +1164,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1159,7 +1175,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1170,7 +1186,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1190,14 +1206,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2831158A-D169-49BB-9942-2243EC476E43}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1208,7 +1224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1219,7 +1235,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1230,7 +1246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1241,7 +1257,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1252,7 +1268,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1263,7 +1279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1274,7 +1290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1285,7 +1301,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1296,7 +1312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1307,7 +1323,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1318,7 +1334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1329,7 +1345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1348,13 +1364,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA1DF80-10FA-482E-96C0-ACB00E266B8C}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1365,7 +1381,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1376,7 +1392,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1387,7 +1403,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1398,7 +1414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1409,7 +1425,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1420,7 +1436,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1436,14 +1452,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27973165-7DE8-4261-971F-5AF0868835AC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1465,13 +1481,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="C5" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="D7" t="s">
         <v>114</v>
       </c>
@@ -1485,14 +1501,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D74D1B-C955-4ECC-9715-1FCC698B0F13}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1503,7 +1519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1514,7 +1530,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -1533,14 +1549,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF806FA6-453F-48DB-A77C-F9ADAC509201}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1551,7 +1567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1562,7 +1578,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1573,7 +1589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1584,7 +1600,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1595,7 +1611,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1606,7 +1622,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1617,7 +1633,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1628,7 +1644,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1648,13 +1664,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA15B4A-9A74-424C-B76B-FE1349821083}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1665,7 +1681,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1676,7 +1692,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1687,7 +1703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1698,7 +1714,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1709,7 +1725,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1720,7 +1736,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1731,7 +1747,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1742,7 +1758,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1753,10 +1769,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="C10" s="9"/>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7">
       <c r="G19" t="s">
         <v>116</v>
       </c>
@@ -1773,13 +1789,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF9EC96-B84F-4905-9DD7-95EF3BF23A01}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1790,7 +1806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1801,7 +1817,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1812,7 +1828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1823,7 +1839,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1834,7 +1850,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1845,7 +1861,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1856,7 +1872,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1867,7 +1883,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1878,7 +1894,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7">
       <c r="G19" t="s">
         <v>116</v>
       </c>
@@ -1891,13 +1907,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9BCD66-1D37-42BA-8077-A6306C929076}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1908,7 +1924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1919,7 +1935,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1930,7 +1946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1941,7 +1957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1952,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1963,7 +1979,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1983,13 +1999,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2004B323-1D53-4498-A3AF-7A7A004D18A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2000,7 +2016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2011,7 +2027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2022,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2033,7 +2049,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2044,7 +2060,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2055,7 +2071,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2066,7 +2082,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2077,7 +2093,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2088,7 +2104,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2099,7 +2115,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2110,7 +2126,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2121,7 +2137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2140,13 +2156,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99414344-EAF9-427C-9BB0-C0063BEEA389}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2157,7 +2173,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2168,7 +2184,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2179,7 +2195,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2190,7 +2206,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2201,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2212,7 +2228,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2232,13 +2248,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FAE8E0-2777-4BC9-8D4C-85DD911170A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2249,7 +2265,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2260,7 +2276,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2271,7 +2287,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2282,7 +2298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2293,7 +2309,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2304,7 +2320,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2323,14 +2339,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0F4E67-C3F8-4D56-99A2-4C13A82795BC}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2341,7 +2357,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2352,7 +2368,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2363,7 +2379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2374,7 +2390,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2385,7 +2401,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2396,7 +2412,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2407,7 +2423,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2418,7 +2434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2429,7 +2445,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2440,7 +2456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2451,7 +2467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2462,7 +2478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -2473,7 +2489,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -2484,7 +2500,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2495,7 +2511,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -2506,7 +2522,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -2517,7 +2533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -2528,7 +2544,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -2539,7 +2555,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -2558,14 +2574,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA439DA5-D0A5-4AAC-AAE2-4792499148E8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2576,7 +2592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2596,14 +2612,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C85660-11FF-42F8-8499-AE3BC3F291AB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2614,7 +2630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2625,7 +2641,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2636,7 +2652,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2647,7 +2663,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2667,13 +2683,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4E8202-CEB6-47CB-B42D-44799C100468}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2684,7 +2700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2695,7 +2711,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2706,7 +2722,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2725,14 +2741,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9B08E7-9F9B-487C-8014-9A20D47C3661}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2743,7 +2759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2754,7 +2770,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2765,7 +2781,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2784,13 +2800,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A47C31-D254-4F2E-A2A3-03DE0C58DF3D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.109375" customWidth="1"/>
+    <col min="3" max="3" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2801,7 +2817,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2812,7 +2828,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2832,14 +2848,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982A2D4F-725B-462F-A6F0-CD37025EE141}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2850,7 +2866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2861,7 +2877,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2872,7 +2888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2883,7 +2899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2894,7 +2910,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2905,7 +2921,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2916,7 +2932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2927,7 +2943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2938,7 +2954,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2949,7 +2965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2960,7 +2976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2971,7 +2987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -2982,7 +2998,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -2993,7 +3009,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -3004,7 +3020,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -3015,7 +3031,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -3034,18 +3050,18 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B322793F-1508-4954-A96D-E508DE6F98E2}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3068,7 +3084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3091,7 +3107,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3111,7 +3127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3131,7 +3147,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3145,82 +3161,82 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="E6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="E7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="E8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="E9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="E10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="E11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="E12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="E13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="E14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="E15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="E16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:5">
       <c r="E17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:5">
       <c r="E18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:5">
       <c r="E19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:5">
       <c r="E20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>51</v>
       </c>
@@ -3233,13 +3249,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22FE06-6BB5-4AD3-99B5-1EB5C931464E}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3250,7 +3266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3261,7 +3277,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3272,7 +3288,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3283,7 +3299,7 @@
         <v>-3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3294,7 +3310,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3305,7 +3321,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3316,7 +3332,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3327,7 +3343,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3338,7 +3354,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3357,13 +3373,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC78B46-40A0-4CB8-9763-6E7E631A0C48}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3374,7 +3390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3385,7 +3401,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3407,7 +3423,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3418,7 +3434,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3429,7 +3445,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3440,7 +3456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3451,7 +3467,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3462,7 +3478,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3473,7 +3489,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3484,7 +3500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3495,7 +3511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3514,13 +3530,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41D0EB0-7F8B-4D12-B4E4-19E9A0280072}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3531,7 +3547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3542,7 +3558,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3553,7 +3569,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3564,7 +3580,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3575,7 +3591,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3586,7 +3602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3606,14 +3622,14 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C57387-E763-4AE4-BC73-76B2CFD5660F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="3" max="3" width="49.88671875" customWidth="1"/>
+    <col min="3" max="3" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3624,7 +3640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3635,7 +3651,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3646,7 +3662,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3657,7 +3673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3668,7 +3684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3679,7 +3695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3698,14 +3714,14 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D4D7BD-E259-420F-B57C-97553341CA40}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3716,7 +3732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3727,7 +3743,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3738,7 +3754,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3749,7 +3765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3760,7 +3776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3771,7 +3787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3790,14 +3806,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55B1D96-CAB9-429D-B308-AD4E2102C9F9}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.88671875" customWidth="1"/>
-    <col min="2" max="2" width="34.109375" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="2" max="2" width="34.1640625" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3808,7 +3824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3819,7 +3835,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3830,7 +3846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3841,7 +3857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3852,7 +3868,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3863,7 +3879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3882,13 +3898,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7667ECB5-3242-40AD-A99C-E440169044C4}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3899,7 +3915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3910,7 +3926,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3921,7 +3937,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3932,7 +3948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3943,7 +3959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3954,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3974,12 +3990,12 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F77D14-FAE8-4C97-9497-A25BE1D39BA7}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3990,7 +4006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4001,7 +4017,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4012,7 +4028,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4023,7 +4039,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4034,7 +4050,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4045,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4064,13 +4080,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7169A81-756B-4781-84B9-B53F8E72B1D8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4081,7 +4097,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4092,7 +4108,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4103,7 +4119,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4114,7 +4130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4125,7 +4141,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4136,7 +4152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4155,13 +4171,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4DB144-605B-4F5E-B562-9E0F0423D523}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4172,7 +4188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4183,7 +4199,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4194,7 +4210,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4205,7 +4221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4216,7 +4232,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4227,7 +4243,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4246,13 +4262,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F3B454-4DBA-4E9B-A949-C34CD2C245D5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4263,7 +4279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4274,7 +4290,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4285,7 +4301,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4296,7 +4312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4307,7 +4323,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4318,7 +4334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4337,13 +4353,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB64170-7C6A-43D2-B9DF-131AC457E710}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4354,7 +4370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4365,7 +4381,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4376,7 +4392,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4387,7 +4403,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="39.75" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4398,10 +4414,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="39.75" customHeight="1">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
     </row>
@@ -4414,13 +4430,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9268CDBE-0606-4B65-A8F6-04136D2C40DC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4431,7 +4447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4442,7 +4458,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4453,7 +4469,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4464,7 +4480,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4475,7 +4491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4486,7 +4502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4505,9 +4521,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C04786-5DC5-40FD-8EF4-0A4E5EC57EDB}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4518,7 +4534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4529,7 +4545,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4540,7 +4556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4559,13 +4575,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB900D6-DDA0-4FE5-BFF4-CF0C76900E85}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="26.1640625" customWidth="1"/>
+    <col min="3" max="3" width="38.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4576,7 +4592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4587,7 +4603,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4598,7 +4614,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4609,7 +4625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4620,7 +4636,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4631,18 +4647,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="16">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C7" s="12" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4653,38 +4669,41 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="C9" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="7:7">
       <c r="G20" t="s">
         <v>116</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{CAC69FAC-885C-D547-9C7B-E50756A3FF96}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE6FFDD-86CC-47A1-A159-E67815015993}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4695,7 +4714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4706,7 +4725,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4717,7 +4736,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4728,7 +4747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4739,7 +4758,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4750,7 +4769,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4761,7 +4780,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4772,7 +4791,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4791,14 +4810,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6C3290-90D3-4091-A830-4534FC405EA9}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4809,7 +4828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4820,7 +4839,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4831,7 +4850,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4842,7 +4861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4853,7 +4872,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4864,7 +4883,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4875,7 +4894,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4886,7 +4905,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4905,9 +4924,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{044B56D1-696B-4348-B6D7-1D9D0FC3A624}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4918,7 +4937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4929,7 +4948,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4940,7 +4959,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4951,7 +4970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4962,7 +4981,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4973,7 +4992,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4984,7 +5003,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4995,7 +5014,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jitendrapisal/reiProjects/product-automation/govgrants-product-automation/src/main/resources/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD9C9B1-31F1-9047-ADD7-26F99A9AFCE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F47004-FE75-4748-AB89-53EF2BE2C52F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5720" yWindow="7880" windowWidth="23260" windowHeight="12580" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="130">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -450,7 +450,10 @@
     <t>Basic Field Grant Office</t>
   </si>
   <si>
-    <t>Bankers Small Business Community Development Corporation Of California</t>
+    <t>Southside Community Criminal Justice Board</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> None</t>
   </si>
 </sst>
 </file>
@@ -519,10 +522,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00396B"/>
+      <name val="Inherit"/>
     </font>
   </fonts>
   <fills count="2">
@@ -569,7 +572,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -886,9 +891,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62ACE97-36F7-4E73-A259-A264DD733BB1}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -956,7 +961,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A057E164-C642-4069-AA67-BFDDC1682771}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1047,11 +1052,11 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69DD06D-7A8F-4C83-860C-E6A58CC62982}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1078,7 +1083,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
@@ -1206,11 +1211,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2831158A-D169-49BB-9942-2243EC476E43}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1364,10 +1369,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA1DF80-10FA-482E-96C0-ACB00E266B8C}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1452,11 +1457,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27973165-7DE8-4261-971F-5AF0868835AC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1501,11 +1506,11 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D74D1B-C955-4ECC-9715-1FCC698B0F13}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1549,10 +1554,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF806FA6-453F-48DB-A77C-F9ADAC509201}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1664,10 +1669,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA15B4A-9A74-424C-B76B-FE1349821083}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.1640625" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1789,10 +1794,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF9EC96-B84F-4905-9DD7-95EF3BF23A01}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.1640625" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1907,10 +1912,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9BCD66-1D37-42BA-8077-A6306C929076}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1999,7 +2004,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2004B323-1D53-4498-A3AF-7A7A004D18A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -2156,9 +2161,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99414344-EAF9-427C-9BB0-C0063BEEA389}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2248,7 +2253,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FAE8E0-2777-4BC9-8D4C-85DD911170A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -2339,9 +2344,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0F4E67-C3F8-4D56-99A2-4C13A82795BC}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2574,10 +2579,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA439DA5-D0A5-4AAC-AAE2-4792499148E8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2612,7 +2617,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C85660-11FF-42F8-8499-AE3BC3F291AB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
@@ -2683,7 +2688,7 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4E8202-CEB6-47CB-B42D-44799C100468}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
@@ -2741,7 +2746,7 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9B08E7-9F9B-487C-8014-9A20D47C3661}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
@@ -2800,10 +2805,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A47C31-D254-4F2E-A2A3-03DE0C58DF3D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.1640625" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2848,9 +2853,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982A2D4F-725B-462F-A6F0-CD37025EE141}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -3050,13 +3055,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B322793F-1508-4954-A96D-E508DE6F98E2}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
@@ -3249,10 +3254,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22FE06-6BB5-4AD3-99B5-1EB5C931464E}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3373,9 +3378,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC78B46-40A0-4CB8-9763-6E7E631A0C48}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3530,9 +3535,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41D0EB0-7F8B-4D12-B4E4-19E9A0280072}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3622,11 +3627,11 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C57387-E763-4AE4-BC73-76B2CFD5660F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="3" max="3" width="49.83203125" customWidth="1"/>
+    <col min="3" max="3" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3714,7 +3719,7 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D4D7BD-E259-420F-B57C-97553341CA40}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
@@ -3806,10 +3811,10 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55B1D96-CAB9-429D-B308-AD4E2102C9F9}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.1640625" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3898,7 +3903,7 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7667ECB5-3242-40AD-A99C-E440169044C4}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -3990,7 +3995,7 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F77D14-FAE8-4C97-9497-A25BE1D39BA7}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
   </cols>
@@ -4080,9 +4085,9 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7169A81-756B-4781-84B9-B53F8E72B1D8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4171,7 +4176,7 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4DB144-605B-4F5E-B562-9E0F0423D523}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -4262,7 +4267,7 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F3B454-4DBA-4E9B-A949-C34CD2C245D5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -4353,10 +4358,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB64170-7C6A-43D2-B9DF-131AC457E710}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4430,7 +4435,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9268CDBE-0606-4B65-A8F6-04136D2C40DC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -4521,7 +4526,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C04786-5DC5-40FD-8EF4-0A4E5EC57EDB}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -4575,10 +4580,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB900D6-DDA0-4FE5-BFF4-CF0C76900E85}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.1640625" customWidth="1"/>
-    <col min="3" max="3" width="38.83203125" customWidth="1"/>
+    <col min="2" max="2" width="26.109375" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4599,7 +4604,7 @@
       <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>119</v>
       </c>
     </row>
@@ -4647,7 +4652,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4697,10 +4702,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE6FFDD-86CC-47A1-A159-E67815015993}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4810,11 +4815,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6C3290-90D3-4091-A830-4534FC405EA9}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4924,7 +4929,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{044B56D1-696B-4348-B6D7-1D9D0FC3A624}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F47004-FE75-4748-AB89-53EF2BE2C52F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F8791D-FE8F-43D2-AF51-C28E3B4AD6D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="11" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -453,14 +453,14 @@
     <t>Southside Community Criminal Justice Board</t>
   </si>
   <si>
-    <t xml:space="preserve"> None</t>
+    <t>fieldGranteeMatch__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,12 +521,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF00396B"/>
-      <name val="Inherit"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -549,7 +543,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -572,9 +566,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -891,13 +882,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62ACE97-36F7-4E73-A259-A264DD733BB1}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -908,7 +899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -919,7 +910,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -930,7 +921,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -941,7 +932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -961,13 +952,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A057E164-C642-4069-AA67-BFDDC1682771}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -978,7 +969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -989,7 +980,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1000,7 +991,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1011,7 +1002,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1022,7 +1013,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1033,7 +1024,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1052,14 +1043,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69DD06D-7A8F-4C83-860C-E6A58CC62982}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1070,7 +1061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1081,18 +1072,18 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>129</v>
-      </c>
-      <c r="B3" t="s">
-        <v>85</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1103,7 +1094,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1114,7 +1105,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1125,7 +1116,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1136,7 +1127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1147,7 +1138,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1158,7 +1149,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1169,7 +1160,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1180,7 +1171,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1191,7 +1182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1211,14 +1202,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2831158A-D169-49BB-9942-2243EC476E43}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1240,7 +1231,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1251,7 +1242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1262,7 +1253,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1273,7 +1264,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1284,7 +1275,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1295,7 +1286,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1306,7 +1297,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1317,7 +1308,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1328,7 +1319,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1339,7 +1330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1350,7 +1341,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1369,13 +1360,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA1DF80-10FA-482E-96C0-ACB00E266B8C}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1386,7 +1377,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1397,7 +1388,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1408,7 +1399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1419,7 +1410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1430,7 +1421,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1441,7 +1432,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1457,14 +1448,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27973165-7DE8-4261-971F-5AF0868835AC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1486,13 +1477,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C5" s="6"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
         <v>114</v>
       </c>
@@ -1506,14 +1497,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D74D1B-C955-4ECC-9715-1FCC698B0F13}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1524,7 +1515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1535,7 +1526,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -1554,14 +1545,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF806FA6-453F-48DB-A77C-F9ADAC509201}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1572,7 +1563,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1583,7 +1574,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1594,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1605,7 +1596,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1616,7 +1607,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1627,7 +1618,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1638,7 +1629,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1649,7 +1640,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1669,13 +1660,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA15B4A-9A74-424C-B76B-FE1349821083}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1686,7 +1677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1697,7 +1688,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1708,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1719,7 +1710,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1730,7 +1721,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1741,7 +1732,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1752,7 +1743,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1763,7 +1754,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1774,10 +1765,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="9"/>
     </row>
-    <row r="19" spans="7:7">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19" t="s">
         <v>116</v>
       </c>
@@ -1794,13 +1785,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF9EC96-B84F-4905-9DD7-95EF3BF23A01}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1811,7 +1802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1822,7 +1813,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1833,7 +1824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1844,7 +1835,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1855,18 +1846,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="C6" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1877,7 +1868,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1888,7 +1879,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1899,7 +1890,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="7:7">
+    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G19" t="s">
         <v>116</v>
       </c>
@@ -1912,13 +1903,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9BCD66-1D37-42BA-8077-A6306C929076}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1929,7 +1920,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1940,7 +1931,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1951,7 +1942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1962,7 +1953,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1973,7 +1964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1984,7 +1975,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2004,13 +1995,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2004B323-1D53-4498-A3AF-7A7A004D18A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2021,7 +2012,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2032,7 +2023,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2043,7 +2034,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2054,7 +2045,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2065,7 +2056,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2076,7 +2067,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2087,7 +2078,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2098,7 +2089,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2109,7 +2100,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2120,7 +2111,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2131,7 +2122,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2142,7 +2133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2161,13 +2152,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99414344-EAF9-427C-9BB0-C0063BEEA389}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2178,7 +2169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2189,7 +2180,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2200,7 +2191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2211,7 +2202,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2222,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2233,7 +2224,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2253,13 +2244,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FAE8E0-2777-4BC9-8D4C-85DD911170A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2270,7 +2261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2281,7 +2272,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2292,7 +2283,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2303,7 +2294,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2314,7 +2305,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2325,7 +2316,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2344,14 +2335,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0F4E67-C3F8-4D56-99A2-4C13A82795BC}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2362,7 +2353,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2373,7 +2364,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2384,7 +2375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2395,7 +2386,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2406,7 +2397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2417,7 +2408,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2428,7 +2419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2439,7 +2430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2450,7 +2441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2461,7 +2452,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2472,7 +2463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2483,7 +2474,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -2494,7 +2485,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -2505,7 +2496,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2516,7 +2507,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -2527,7 +2518,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -2538,7 +2529,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -2549,7 +2540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -2560,7 +2551,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -2579,14 +2570,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA439DA5-D0A5-4AAC-AAE2-4792499148E8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2597,7 +2588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2617,14 +2608,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C85660-11FF-42F8-8499-AE3BC3F291AB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2635,7 +2626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2646,7 +2637,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2657,7 +2648,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2668,7 +2659,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2688,13 +2679,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4E8202-CEB6-47CB-B42D-44799C100468}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2696,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2716,7 +2707,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2727,7 +2718,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2746,14 +2737,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9B08E7-9F9B-487C-8014-9A20D47C3661}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2764,7 +2755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2775,7 +2766,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2786,7 +2777,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2805,13 +2796,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A47C31-D254-4F2E-A2A3-03DE0C58DF3D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2822,7 +2813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2833,7 +2824,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2853,14 +2844,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982A2D4F-725B-462F-A6F0-CD37025EE141}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2871,7 +2862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2882,7 +2873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2893,7 +2884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2904,7 +2895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2915,7 +2906,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2926,7 +2917,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2937,7 +2928,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2948,7 +2939,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2959,7 +2950,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2970,7 +2961,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2981,7 +2972,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2992,7 +2983,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -3003,7 +2994,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -3014,7 +3005,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -3025,7 +3016,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -3036,7 +3027,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -3055,7 +3046,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B322793F-1508-4954-A96D-E508DE6F98E2}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -3066,7 +3057,7 @@
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3089,7 +3080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3112,7 +3103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3132,7 +3123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3152,7 +3143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3166,82 +3157,82 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="E16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="5:5">
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="5:5">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="5:5">
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="5:5">
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="5:5">
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" t="s">
         <v>51</v>
       </c>
@@ -3254,13 +3245,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22FE06-6BB5-4AD3-99B5-1EB5C931464E}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3271,7 +3262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3282,7 +3273,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3293,7 +3284,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3304,7 +3295,7 @@
         <v>-3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3315,7 +3306,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3326,7 +3317,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3337,7 +3328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3348,7 +3339,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3359,7 +3350,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3378,13 +3369,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC78B46-40A0-4CB8-9763-6E7E631A0C48}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3395,7 +3386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3406,7 +3397,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3417,7 +3408,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3428,7 +3419,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3439,7 +3430,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3450,7 +3441,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3461,7 +3452,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3472,7 +3463,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3483,7 +3474,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3494,7 +3485,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3505,7 +3496,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3516,7 +3507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3535,13 +3526,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41D0EB0-7F8B-4D12-B4E4-19E9A0280072}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3552,7 +3543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3563,7 +3554,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3574,7 +3565,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3585,7 +3576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3596,7 +3587,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3607,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3627,14 +3618,14 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C57387-E763-4AE4-BC73-76B2CFD5660F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
     <col min="3" max="3" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3645,7 +3636,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3656,7 +3647,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3667,7 +3658,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3678,7 +3669,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3689,7 +3680,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3700,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3719,14 +3710,14 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D4D7BD-E259-420F-B57C-97553341CA40}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3737,7 +3728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3748,7 +3739,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3759,7 +3750,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3770,7 +3761,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3781,7 +3772,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3792,7 +3783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3811,14 +3802,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55B1D96-CAB9-429D-B308-AD4E2102C9F9}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3829,7 +3820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3840,7 +3831,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3851,7 +3842,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3862,7 +3853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3873,7 +3864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3884,7 +3875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3903,13 +3894,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7667ECB5-3242-40AD-A99C-E440169044C4}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3920,7 +3911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3931,7 +3922,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3942,7 +3933,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3953,7 +3944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3964,7 +3955,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3975,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3995,12 +3986,12 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F77D14-FAE8-4C97-9497-A25BE1D39BA7}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4011,7 +4002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4022,7 +4013,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4033,7 +4024,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4044,7 +4035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4055,7 +4046,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4066,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4085,13 +4076,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7169A81-756B-4781-84B9-B53F8E72B1D8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4102,7 +4093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4113,7 +4104,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4124,7 +4115,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4135,7 +4126,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4146,7 +4137,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4157,7 +4148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4176,13 +4167,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4DB144-605B-4F5E-B562-9E0F0423D523}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4193,7 +4184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4204,7 +4195,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4215,7 +4206,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4226,7 +4217,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4237,7 +4228,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4248,7 +4239,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4267,13 +4258,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F3B454-4DBA-4E9B-A949-C34CD2C245D5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4295,7 +4286,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4306,7 +4297,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4317,7 +4308,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4328,7 +4319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4339,7 +4330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4358,13 +4349,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB64170-7C6A-43D2-B9DF-131AC457E710}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4375,7 +4366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4386,7 +4377,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4397,7 +4388,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4408,7 +4399,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.75" customHeight="1">
+    <row r="5" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4419,10 +4410,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.75" customHeight="1">
+    <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
     </row>
@@ -4435,13 +4426,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9268CDBE-0606-4B65-A8F6-04136D2C40DC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4452,7 +4443,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4463,7 +4454,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4474,7 +4465,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4485,7 +4476,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4496,7 +4487,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4507,7 +4498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4526,9 +4517,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C04786-5DC5-40FD-8EF4-0A4E5EC57EDB}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4539,7 +4530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4550,7 +4541,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4561,7 +4552,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4580,13 +4571,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB900D6-DDA0-4FE5-BFF4-CF0C76900E85}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4597,7 +4588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4608,7 +4599,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4619,7 +4610,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4630,7 +4621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4641,7 +4632,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4652,18 +4643,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4674,7 +4665,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4685,7 +4676,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="7:7">
+    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
       <c r="G20" t="s">
         <v>116</v>
       </c>
@@ -4702,13 +4693,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE6FFDD-86CC-47A1-A159-E67815015993}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4719,7 +4710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4730,7 +4721,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4741,7 +4732,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4752,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4763,7 +4754,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4774,18 +4765,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4796,33 +4787,37 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" t="s">
-        <v>78</v>
+      <c r="C9" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{C6F488BA-9561-4694-8515-4E80A5F62A10}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6C3290-90D3-4091-A830-4534FC405EA9}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4833,7 +4828,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4844,7 +4839,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4855,7 +4850,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4866,7 +4861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4877,7 +4872,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4888,18 +4883,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4910,18 +4905,21 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>77</v>
       </c>
-      <c r="C9" t="s">
-        <v>78</v>
+      <c r="C9" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{8F75DDB5-D275-484F-AC89-BAFD75CDBB34}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4929,9 +4927,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{044B56D1-696B-4348-B6D7-1D9D0FC3A624}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4942,7 +4940,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4953,7 +4951,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4964,7 +4962,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4975,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4986,7 +4984,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4997,18 +4995,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7" s="9" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -5019,7 +5017,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F8791D-FE8F-43D2-AF51-C28E3B4AD6D4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED29ACF-D395-4B1E-998E-1649FB106438}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="6" activeTab="11" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="13" activeTab="17" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1875,8 +1875,8 @@
       <c r="B8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" t="s">
-        <v>78</v>
+      <c r="C8" s="11" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1896,6 +1896,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C8" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{9CBF36DE-4B3A-4BB6-A4BE-813F9EE8E219}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED29ACF-D395-4B1E-998E-1649FB106438}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B602120A-4B68-4DBF-A834-8B16C0F5E175}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="13" activeTab="17" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="133">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -451,6 +451,15 @@
   </si>
   <si>
     <t>Southside Community Criminal Justice Board</t>
+  </si>
+  <si>
+    <t>SAN DIEGO ELECTRICAL TRAINING TRUST Partner User</t>
+  </si>
+  <si>
+    <t>Automation Execution Award    </t>
+  </si>
+  <si>
+    <t>Non-Construction</t>
   </si>
   <si>
     <t>fieldGranteeMatch__c</t>
@@ -460,7 +469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +530,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00396B"/>
+      <name val="Helvetica"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -543,7 +564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -566,6 +587,10 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1077,7 +1102,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -4577,7 +4602,7 @@
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
+    <col min="3" max="3" width="47.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -4598,8 +4623,8 @@
       <c r="B2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>119</v>
+      <c r="C2" s="12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -4643,7 +4668,7 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -4653,8 +4678,8 @@
       <c r="B7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C7" t="s">
-        <v>128</v>
+      <c r="C7" s="13" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -4676,7 +4701,7 @@
         <v>77</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.3">
@@ -4686,7 +4711,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C9" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{CAC69FAC-885C-D547-9C7B-E50756A3FF96}"/>
+    <hyperlink ref="C9" r:id="rId1" tooltip="Test Automation Organization" display="https://lsc--qa--c.visualforce.com/0010r00000J41OFAAZ" xr:uid="{BFFE83F1-5A18-4462-A8C3-F4D48C67EC51}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B602120A-4B68-4DBF-A834-8B16C0F5E175}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7403C7D8-EA89-4B9B-ACB1-5B3C7FB6AA04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="5" activeTab="5" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="12" activeTab="17" xr2:uid="{10FEA7AB-10C6-4A3F-BF77-BE44F0EFE02D}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -469,7 +469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,6 +542,12 @@
       <color rgb="FF00396B"/>
       <name val="Helvetica"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF00396B"/>
+      <name val="&amp;quot"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -564,7 +570,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -591,6 +597,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -907,13 +916,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62ACE97-36F7-4E73-A259-A264DD733BB1}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -924,7 +933,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -935,7 +944,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -946,7 +955,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -957,7 +966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -977,13 +986,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A057E164-C642-4069-AA67-BFDDC1682771}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -994,7 +1003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1005,7 +1014,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1016,7 +1025,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1027,7 +1036,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1038,7 +1047,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1068,14 +1077,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D69DD06D-7A8F-4C83-860C-E6A58CC62982}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1086,7 +1095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1097,7 +1106,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1108,7 +1117,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1119,7 +1128,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1130,7 +1139,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1141,7 +1150,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1152,7 +1161,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1163,7 +1172,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1174,7 +1183,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1185,7 +1194,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1196,7 +1205,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1207,7 +1216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1227,14 +1236,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2831158A-D169-49BB-9942-2243EC476E43}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
     <col min="2" max="2" width="29.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1245,7 +1254,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1256,7 +1265,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1267,7 +1276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1278,7 +1287,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1289,7 +1298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1300,7 +1309,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1322,7 +1331,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1333,7 +1342,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1344,7 +1353,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1355,7 +1364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1366,7 +1375,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1385,13 +1394,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDA1DF80-10FA-482E-96C0-ACB00E266B8C}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -1402,7 +1411,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1413,7 +1422,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1424,7 +1433,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -1435,7 +1444,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -1446,7 +1455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1457,7 +1466,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>82</v>
       </c>
@@ -1473,14 +1482,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27973165-7DE8-4261-971F-5AF0868835AC}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1491,7 +1500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1502,13 +1511,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4">
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4">
       <c r="C5" s="6"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4">
       <c r="D7" t="s">
         <v>114</v>
       </c>
@@ -1522,14 +1531,14 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D74D1B-C955-4ECC-9715-1FCC698B0F13}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1540,7 +1549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1551,7 +1560,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -1570,14 +1579,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF806FA6-453F-48DB-A77C-F9ADAC509201}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1588,7 +1597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1599,7 +1608,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1610,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1621,7 +1630,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1632,7 +1641,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1643,7 +1652,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1654,7 +1663,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1665,7 +1674,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1685,13 +1694,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA15B4A-9A74-424C-B76B-FE1349821083}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1702,7 +1711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1713,7 +1722,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1724,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1735,7 +1744,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1746,7 +1755,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1757,7 +1766,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1768,7 +1777,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1779,7 +1788,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1790,10 +1799,10 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="C10" s="9"/>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7">
       <c r="G19" t="s">
         <v>116</v>
       </c>
@@ -1810,13 +1819,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EF9EC96-B84F-4905-9DD7-95EF3BF23A01}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
+    <col min="3" max="3" width="50.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1827,7 +1836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1838,7 +1847,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1849,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1860,7 +1869,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1871,18 +1880,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C6" s="14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1893,18 +1902,18 @@
         <v>107</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1915,29 +1924,27 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="7:7">
       <c r="G19" t="s">
         <v>116</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{9CBF36DE-4B3A-4BB6-A4BE-813F9EE8E219}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A9BCD66-1D37-42BA-8077-A6306C929076}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1948,7 +1955,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1959,7 +1966,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1970,7 +1977,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1981,7 +1988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1992,7 +1999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2003,7 +2010,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2023,13 +2030,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2004B323-1D53-4498-A3AF-7A7A004D18A4}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2040,7 +2047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2051,7 +2058,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2062,7 +2069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2073,7 +2080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2084,7 +2091,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2095,7 +2102,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2106,7 +2113,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -2117,7 +2124,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2128,7 +2135,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2139,7 +2146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -2150,7 +2157,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -2161,7 +2168,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -2180,13 +2187,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99414344-EAF9-427C-9BB0-C0063BEEA389}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2197,7 +2204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2208,7 +2215,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2219,7 +2226,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2230,7 +2237,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2241,7 +2248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2252,7 +2259,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2272,13 +2279,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26FAE8E0-2777-4BC9-8D4C-85DD911170A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2289,7 +2296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2300,7 +2307,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2311,7 +2318,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2322,7 +2329,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2333,7 +2340,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2344,7 +2351,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2363,14 +2370,14 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0F4E67-C3F8-4D56-99A2-4C13A82795BC}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2381,7 +2388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2392,7 +2399,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2403,7 +2410,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2414,7 +2421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2425,7 +2432,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2436,7 +2443,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2447,7 +2454,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2458,7 +2465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2469,7 +2476,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2480,7 +2487,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2491,7 +2498,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -2502,7 +2509,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -2513,7 +2520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -2524,7 +2531,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2535,7 +2542,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -2546,7 +2553,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -2557,7 +2564,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>96</v>
       </c>
@@ -2568,7 +2575,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>96</v>
       </c>
@@ -2579,7 +2586,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>96</v>
       </c>
@@ -2598,14 +2605,14 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA439DA5-D0A5-4AAC-AAE2-4792499148E8}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2616,7 +2623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2636,14 +2643,14 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C85660-11FF-42F8-8499-AE3BC3F291AB}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2654,7 +2661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2665,7 +2672,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2676,7 +2683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2687,7 +2694,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2707,13 +2714,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B4E8202-CEB6-47CB-B42D-44799C100468}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2724,7 +2731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2735,7 +2742,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2746,7 +2753,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2765,14 +2772,14 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E9B08E7-9F9B-487C-8014-9A20D47C3661}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,7 +2790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2794,7 +2801,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2805,7 +2812,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2824,13 +2831,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99A47C31-D254-4F2E-A2A3-03DE0C58DF3D}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2841,7 +2848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2852,7 +2859,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2872,14 +2879,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{982A2D4F-725B-462F-A6F0-CD37025EE141}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2890,7 +2897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -2901,7 +2908,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>96</v>
       </c>
@@ -2912,7 +2919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>96</v>
       </c>
@@ -2923,7 +2930,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>96</v>
       </c>
@@ -2934,7 +2941,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>96</v>
       </c>
@@ -2945,7 +2952,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>96</v>
       </c>
@@ -2956,7 +2963,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>96</v>
       </c>
@@ -2967,7 +2974,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>96</v>
       </c>
@@ -2978,7 +2985,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2989,7 +2996,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -3000,7 +3007,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -3011,7 +3018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -3022,7 +3029,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -3033,7 +3040,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -3044,7 +3051,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -3055,7 +3062,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -3074,7 +3081,7 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B322793F-1508-4954-A96D-E508DE6F98E2}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -3085,7 +3092,7 @@
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -3108,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -3131,7 +3138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -3151,7 +3158,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3171,7 +3178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3185,82 +3192,82 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="E6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="E7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="E8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="E9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="E10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="E11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="E12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="E13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="E14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="E15" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="E16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="5:5">
       <c r="E17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="5:5">
       <c r="E18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="5:5">
       <c r="E19" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="5:5">
       <c r="E20" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>51</v>
       </c>
@@ -3273,13 +3280,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB22FE06-6BB5-4AD3-99B5-1EB5C931464E}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3290,7 +3297,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3301,7 +3308,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3312,7 +3319,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3323,7 +3330,7 @@
         <v>-3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3334,7 +3341,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3345,7 +3352,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3356,7 +3363,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3367,7 +3374,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3378,7 +3385,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3397,13 +3404,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FC78B46-40A0-4CB8-9763-6E7E631A0C48}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3414,7 +3421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3425,7 +3432,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3447,7 +3454,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3458,7 +3465,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3469,7 +3476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3480,7 +3487,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -3491,7 +3498,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -3502,7 +3509,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -3513,7 +3520,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -3524,7 +3531,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -3535,7 +3542,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -3554,13 +3561,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41D0EB0-7F8B-4D12-B4E4-19E9A0280072}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3571,7 +3578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3582,7 +3589,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3593,7 +3600,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3604,7 +3611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3615,7 +3622,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3626,7 +3633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3646,14 +3653,14 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0C57387-E763-4AE4-BC73-76B2CFD5660F}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" customWidth="1"/>
     <col min="3" max="3" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3664,7 +3671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3675,7 +3682,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3686,7 +3693,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3697,7 +3704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3708,7 +3715,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3719,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3738,14 +3745,14 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D4D7BD-E259-420F-B57C-97553341CA40}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
     <col min="2" max="2" width="28.33203125" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3756,7 +3763,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3767,7 +3774,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3778,7 +3785,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3789,7 +3796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3800,7 +3807,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3811,7 +3818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3830,14 +3837,14 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F55B1D96-CAB9-429D-B308-AD4E2102C9F9}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.109375" customWidth="1"/>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3848,7 +3855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3859,7 +3866,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3881,7 +3888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3892,7 +3899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3903,7 +3910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -3922,13 +3929,13 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7667ECB5-3242-40AD-A99C-E440169044C4}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3939,7 +3946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3950,7 +3957,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -3961,7 +3968,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -3972,7 +3979,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3983,7 +3990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -3994,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4014,12 +4021,12 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F77D14-FAE8-4C97-9497-A25BE1D39BA7}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4030,7 +4037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4041,7 +4048,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4052,7 +4059,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4063,7 +4070,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4074,7 +4081,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4085,7 +4092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4104,13 +4111,13 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7169A81-756B-4781-84B9-B53F8E72B1D8}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4121,7 +4128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4132,7 +4139,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4143,7 +4150,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4154,7 +4161,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4165,7 +4172,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4176,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4195,13 +4202,13 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C4DB144-605B-4F5E-B562-9E0F0423D523}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4212,7 +4219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4223,7 +4230,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4234,7 +4241,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4245,7 +4252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4256,7 +4263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4267,7 +4274,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4286,13 +4293,13 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2F3B454-4DBA-4E9B-A949-C34CD2C245D5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4303,7 +4310,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4314,7 +4321,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4325,7 +4332,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4336,7 +4343,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4347,7 +4354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4358,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4377,13 +4384,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCB64170-7C6A-43D2-B9DF-131AC457E710}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4394,7 +4401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4405,7 +4412,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4416,7 +4423,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4427,7 +4434,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="39.75" customHeight="1">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4438,10 +4445,10 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="39.75" customHeight="1">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
     </row>
@@ -4454,13 +4461,13 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9268CDBE-0606-4B65-A8F6-04136D2C40DC}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4471,7 +4478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4482,7 +4489,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4493,7 +4500,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4504,7 +4511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4515,7 +4522,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4526,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4545,9 +4552,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27C04786-5DC5-40FD-8EF4-0A4E5EC57EDB}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4558,7 +4565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4569,7 +4576,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4580,7 +4587,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4599,13 +4606,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB900D6-DDA0-4FE5-BFF4-CF0C76900E85}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26.109375" customWidth="1"/>
     <col min="3" max="3" width="47.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4616,7 +4623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4627,7 +4634,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4638,7 +4645,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4649,7 +4656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4660,7 +4667,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4671,7 +4678,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4682,7 +4689,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4693,7 +4700,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4704,7 +4711,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="7:7">
       <c r="G20" t="s">
         <v>116</v>
       </c>
@@ -4721,13 +4728,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE6FFDD-86CC-47A1-A159-E67815015993}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4738,7 +4745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4749,7 +4756,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4760,7 +4767,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4771,7 +4778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4782,7 +4789,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4793,7 +4800,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4804,7 +4811,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4815,7 +4822,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4838,14 +4845,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB6C3290-90D3-4091-A830-4534FC405EA9}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4856,7 +4863,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4867,7 +4874,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4878,7 +4885,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4889,7 +4896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4900,7 +4907,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -4911,7 +4918,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -4922,7 +4929,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -4933,7 +4940,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -4955,9 +4962,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{044B56D1-696B-4348-B6D7-1D9D0FC3A624}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4968,7 +4975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4979,7 +4986,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5001,7 +5008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -5012,7 +5019,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -5023,7 +5030,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -5034,7 +5041,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -5045,7 +5052,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A4B2A1-B22F-47B3-84E0-6180EB2B323E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419FEF93-22FC-46CE-8724-DD2C01B6FDFF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="43" activeTab="44" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="132">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -444,6 +444,27 @@
   </si>
   <si>
     <t>fieldProjectTitle__c</t>
+  </si>
+  <si>
+    <t>fieldGrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>fieldProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldBudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>fieldProgram__c</t>
+  </si>
+  <si>
+    <t>Automation Internal Org</t>
+  </si>
+  <si>
+    <t>fieldExternalOrganization__c</t>
   </si>
 </sst>
 </file>
@@ -2517,8 +2538,8 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>67</v>
+      <c r="B2" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>95</v>
@@ -2528,8 +2549,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>68</v>
+      <c r="B3" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -2539,8 +2560,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>69</v>
+      <c r="B4" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -2550,8 +2571,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>70</v>
+      <c r="B5" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C5" t="s">
         <v>71</v>
@@ -2573,7 +2594,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
         <v>98</v>
@@ -2584,10 +2605,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -5213,8 +5234,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>67</v>
+      <c r="B3" s="3" t="s">
+        <v>125</v>
       </c>
       <c r="C3" t="s">
         <v>95</v>
@@ -5224,8 +5245,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>68</v>
+      <c r="B4" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5235,8 +5256,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>69</v>
+      <c r="B5" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5246,8 +5267,8 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>70</v>
+      <c r="B6" s="3" t="s">
+        <v>128</v>
       </c>
       <c r="C6" t="s">
         <v>71</v>
@@ -5268,8 +5289,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>73</v>
+      <c r="B8" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="C8" t="s">
         <v>98</v>
@@ -5279,11 +5300,11 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>74</v>
+      <c r="B9" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="C9" t="s">
-        <v>75</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{419FEF93-22FC-46CE-8724-DD2C01B6FDFF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD325C96-417C-4F36-8C61-AD4014A1C685}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="137">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -465,6 +465,21 @@
   </si>
   <si>
     <t>fieldExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>fieldSubmissionTitle__c</t>
+  </si>
+  <si>
+    <t>fieldScheduleBase__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldFrequency__c</t>
   </si>
 </sst>
 </file>
@@ -922,7 +937,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
         <v>118</v>
@@ -933,7 +948,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
         <v>96</v>
@@ -944,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -2657,7 +2672,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="C2" t="s">
         <v>121</v>
@@ -2668,7 +2683,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -2679,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -2690,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2701,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
         <v>96</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E68872-20AB-410E-826F-CDF198A8431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0634A05A-E9D4-459D-B42C-9E2B2448D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="46" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="17" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="164">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -453,9 +453,6 @@
     <t>fieldProjectPeriodEndDate__c</t>
   </si>
   <si>
-    <t>fieldBudgetCategoryPackage__c</t>
-  </si>
-  <si>
     <t>fieldProgram__c</t>
   </si>
   <si>
@@ -580,6 +577,18 @@
   </si>
   <si>
     <t>Product Sub Recipient Test Organization</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>GrantType__c</t>
+  </si>
+  <si>
+    <t>AllocationLevel__c</t>
   </si>
 </sst>
 </file>
@@ -1067,10 +1076,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1089,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -1100,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
@@ -1111,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -1126,9 +1135,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1214,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1225,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -1240,10 +1249,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1320,7 +1329,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1328,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1339,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -1353,10 +1362,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.54296875" customWidth="1"/>
+    <col min="3" max="3" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1433,7 +1442,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1441,7 +1450,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1452,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>103</v>
@@ -1466,10 +1475,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1491,7 +1500,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1554,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1565,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -1579,11 +1588,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1694,10 +1703,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1808,9 +1817,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1922,7 +1931,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1977,7 +1986,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1988,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -2002,10 +2011,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2069,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -2146,10 +2155,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2157,10 +2166,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2172,10 +2181,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2327,10 +2336,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2338,10 +2347,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2352,9 +2361,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2495,10 +2504,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2506,10 +2515,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2520,10 +2529,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2664,10 +2673,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2675,10 +2684,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2689,10 +2698,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2836,9 +2845,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2858,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2869,7 +2878,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2880,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2891,7 +2900,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2902,7 +2911,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2913,7 +2922,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2924,7 +2933,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2935,7 +2944,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2946,7 +2955,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2957,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2968,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2979,10 +2988,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>148</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2990,10 +2999,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3004,10 +3013,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3070,7 +3079,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3147,10 +3156,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3158,10 +3167,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3172,10 +3181,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3238,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3315,10 +3324,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3326,10 +3335,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -3340,10 +3349,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3406,7 +3415,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3483,10 +3492,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3494,10 +3503,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3508,10 +3517,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="3" max="3" width="35.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3574,7 +3583,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3651,10 +3660,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3662,10 +3671,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3676,10 +3685,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3742,7 +3751,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3819,10 +3828,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3830,10 +3839,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3844,10 +3853,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3910,7 +3919,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3987,10 +3996,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3998,10 +4007,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4012,9 +4021,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4078,7 +4087,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4155,10 +4164,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4166,10 +4175,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4180,9 +4189,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4304,9 +4313,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4370,7 +4379,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4447,10 +4456,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4458,10 +4467,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4472,10 +4481,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4539,7 +4548,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -4616,10 +4625,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4627,10 +4636,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4641,9 +4650,9 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4707,7 +4716,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4784,10 +4793,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4795,10 +4804,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -4809,10 +4818,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4843,10 +4852,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
         <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4854,7 +4863,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4865,7 +4874,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4876,7 +4885,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4887,7 +4896,7 @@
         <v>73</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4898,7 +4907,7 @@
         <v>73</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4913,9 +4922,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4935,7 +4944,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -4946,10 +4955,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C3" t="s">
         <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4957,7 +4966,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4968,7 +4977,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4979,7 +4988,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4990,7 +4999,7 @@
         <v>73</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -5001,7 +5010,7 @@
         <v>73</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -5015,11 +5024,11 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5130,10 +5139,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5252,10 +5261,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5284,8 +5293,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>116</v>
+      <c r="B3" t="s">
+        <v>160</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5295,8 +5304,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>117</v>
+      <c r="B4" t="s">
+        <v>161</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5306,8 +5315,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>118</v>
+      <c r="B5" t="s">
+        <v>67</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
@@ -5318,7 +5327,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5328,8 +5337,8 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>119</v>
+      <c r="B7" t="s">
+        <v>70</v>
       </c>
       <c r="C7" t="s">
         <v>92</v>
@@ -5339,8 +5348,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>120</v>
+      <c r="B8" t="s">
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>72</v>
@@ -5351,7 +5360,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
         <v>108</v>
@@ -5371,9 +5380,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5393,7 +5402,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>112</v>
@@ -5404,7 +5413,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -5415,7 +5424,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5426,7 +5435,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5437,7 +5446,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
@@ -5452,10 +5461,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5474,7 +5483,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -5485,7 +5494,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -5496,7 +5505,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5507,7 +5516,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5518,7 +5527,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
@@ -5533,9 +5542,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5596,7 +5605,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5662,7 +5671,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>101</v>
@@ -5673,7 +5682,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5687,11 +5696,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5923,11 +5932,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5961,11 +5970,11 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6032,10 +6041,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6068,7 +6077,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6090,11 +6099,11 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6127,7 +6136,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6149,10 +6158,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6197,10 +6206,10 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6222,7 +6231,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6244,11 +6253,11 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6446,15 +6455,15 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6645,11 +6654,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6704,11 +6713,11 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6774,7 +6783,7 @@
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6818,10 +6827,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6975,10 +6984,10 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7008,7 +7017,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7041,7 +7050,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7052,7 +7061,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -7067,11 +7076,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7101,7 +7110,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7134,7 +7143,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7145,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7159,11 +7168,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7193,7 +7202,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>97</v>
@@ -7226,7 +7235,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7237,7 +7246,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7251,11 +7260,11 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7285,7 +7294,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>98</v>
@@ -7318,7 +7327,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7329,7 +7338,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7343,7 +7352,7 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7376,7 +7385,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>96</v>
@@ -7409,7 +7418,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7420,7 +7429,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7435,10 +7444,10 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7468,7 +7477,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>99</v>
@@ -7501,7 +7510,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7512,7 +7521,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7526,9 +7535,9 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7559,7 +7568,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7581,7 +7590,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7592,7 +7601,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7606,7 +7615,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7639,7 +7648,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7661,7 +7670,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7672,7 +7681,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7686,7 +7695,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7785,7 +7794,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -7800,7 +7809,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7833,7 +7842,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7866,7 +7875,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7877,7 +7886,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7891,7 +7900,7 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7924,7 +7933,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>97</v>
@@ -7957,7 +7966,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7968,7 +7977,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7982,10 +7991,10 @@
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8096,9 +8105,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8209,7 +8218,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A058B24C-ECE4-4154-B985-11F85C7FD554}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8218,10 +8227,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8279,7 +8288,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8290,7 +8299,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8298,7 +8307,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8306,10 +8315,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8317,10 +8326,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0634A05A-E9D4-459D-B42C-9E2B2448D03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC707ED-A6ED-4258-AA1A-01BFF5AEF63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="17" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="39" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="169">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -477,9 +477,6 @@
     <t>fieldScheduleBase__c</t>
   </si>
   <si>
-    <t>fieldGrantAwardDescription__c</t>
-  </si>
-  <si>
     <t>fieldAddressline2__c</t>
   </si>
   <si>
@@ -589,6 +586,24 @@
   </si>
   <si>
     <t>AllocationLevel__c</t>
+  </si>
+  <si>
+    <t>Addressline2__c</t>
+  </si>
+  <si>
+    <t>ZipCode4Extension__c</t>
+  </si>
+  <si>
+    <t>CongressionalDistrictName__c</t>
+  </si>
+  <si>
+    <t>BudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>NewObligation__c</t>
+  </si>
+  <si>
+    <t>TotalCommitment__c</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1344,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1442,7 +1457,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1500,7 +1515,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2155,10 +2170,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2166,10 +2181,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2336,10 +2351,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2347,10 +2362,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2504,10 +2519,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2515,10 +2530,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2673,10 +2688,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2684,10 +2699,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2867,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2878,7 +2893,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2889,7 +2904,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2900,7 +2915,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2911,7 +2926,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2922,7 +2937,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2933,7 +2948,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2944,7 +2959,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2955,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2966,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2977,7 +2992,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2988,10 +3003,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>147</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2999,10 +3014,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +3094,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3156,10 +3171,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3167,10 +3182,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3247,7 +3262,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3324,10 +3339,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3335,10 +3350,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3415,7 +3430,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3492,10 +3507,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3503,10 +3518,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3583,7 +3598,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3660,10 +3675,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3671,10 +3686,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3751,7 +3766,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3828,10 +3843,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3839,10 +3854,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -3919,7 +3934,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3996,10 +4011,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4007,10 +4022,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4087,7 +4102,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4164,10 +4179,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>147</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4175,10 +4190,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4379,7 +4394,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4456,10 +4471,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4467,10 +4482,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4548,7 +4563,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -4625,10 +4640,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4636,10 +4651,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4716,7 +4731,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4793,10 +4808,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4804,10 +4819,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
         <v>149</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -4852,10 +4867,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
         <v>127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4863,7 +4878,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4874,7 +4889,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4885,7 +4900,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4896,7 +4911,7 @@
         <v>73</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4907,7 +4922,7 @@
         <v>73</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4944,7 +4959,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -4955,10 +4970,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" t="s">
         <v>127</v>
-      </c>
-      <c r="C3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4966,7 +4981,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4977,7 +4992,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>129</v>
+        <v>165</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4987,8 +5002,8 @@
       <c r="A6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>132</v>
+      <c r="B6" t="s">
+        <v>166</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4998,8 +5013,8 @@
       <c r="A7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>155</v>
+      <c r="B7" t="s">
+        <v>167</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -5009,8 +5024,8 @@
       <c r="A8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>156</v>
+      <c r="B8" t="s">
+        <v>168</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -5294,7 +5309,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5305,7 +5320,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6231,7 +6246,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6783,7 +6798,7 @@
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -8307,7 +8322,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8318,7 +8333,7 @@
         <v>118</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8329,7 +8344,7 @@
         <v>119</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC707ED-A6ED-4258-AA1A-01BFF5AEF63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32432797-5E6B-4CC9-AC74-1052668CDC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="39" activeTab="41" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1172,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
@@ -1194,7 +1194,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1227,7 +1227,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1238,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1248,8 +1248,8 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>119</v>
+      <c r="B9" t="s">
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -4563,7 +4563,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -4640,7 +4640,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>151</v>
@@ -4651,7 +4651,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>149</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32432797-5E6B-4CC9-AC74-1052668CDC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E77076B-BCFD-44E2-B137-14D9F5DFEE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="171">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -604,6 +604,12 @@
   </si>
   <si>
     <t>TotalCommitment__c</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -5417,7 +5423,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>112</v>
@@ -5428,7 +5434,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -5439,7 +5445,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5450,7 +5456,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5461,7 +5467,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>
@@ -5498,7 +5504,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -5509,7 +5515,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -5520,7 +5526,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5531,7 +5537,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5542,7 +5548,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
         <v>90</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E77076B-BCFD-44E2-B137-14D9F5DFEE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566BEBA2-A368-4205-BEA4-0242B730B967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="38" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="163">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -462,9 +462,6 @@
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>fieldSubmissionTitle__c</t>
-  </si>
-  <si>
     <t>fieldCalReportingStartDate__c</t>
   </si>
   <si>
@@ -474,27 +471,12 @@
     <t>fieldFrequency__c</t>
   </si>
   <si>
-    <t>fieldScheduleBase__c</t>
-  </si>
-  <si>
-    <t>fieldAddressline2__c</t>
-  </si>
-  <si>
     <t>751  August Lane1</t>
   </si>
   <si>
-    <t>fieldCongressionalDistrictName__c</t>
-  </si>
-  <si>
-    <t>fieldZipCode4Extension__c</t>
-  </si>
-  <si>
     <t>Automation Permanent KPI</t>
   </si>
   <si>
-    <t>fieldBudgetPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>Automation Runtime Bulks Grants Records</t>
   </si>
   <si>
@@ -559,12 +541,6 @@
   </si>
   <si>
     <t>By Applicant</t>
-  </si>
-  <si>
-    <t>fieldNewObligation__c</t>
-  </si>
-  <si>
-    <t>fieldTotalCommitment__c</t>
   </si>
   <si>
     <t>By Applicant and Focus Area</t>
@@ -1119,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>109</v>
@@ -1130,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
         <v>90</v>
@@ -1141,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -1200,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1211,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1350,7 +1326,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1463,7 +1439,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1521,7 +1497,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2007,7 +1983,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -2018,7 +1994,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -2176,10 +2152,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2187,10 +2163,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2357,10 +2333,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2368,10 +2344,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2525,10 +2501,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2536,10 +2512,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2694,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2705,10 +2681,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2888,7 +2864,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2899,7 +2875,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2910,7 +2886,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2921,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2932,7 +2908,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2943,7 +2919,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2954,7 +2930,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2965,7 +2941,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2976,7 +2952,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2987,7 +2963,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2998,7 +2974,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -3009,10 +2985,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3020,10 +2996,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3100,7 +3076,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3177,10 +3153,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3188,10 +3164,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3268,7 +3244,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3345,10 +3321,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3356,10 +3332,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3436,7 +3412,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3513,10 +3489,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3524,10 +3500,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3604,7 +3580,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3681,10 +3657,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>146</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3692,10 +3668,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>148</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3772,7 +3748,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3849,10 +3825,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3860,10 +3836,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3940,7 +3916,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -4017,10 +3993,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4028,10 +4004,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4108,7 +4084,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4185,10 +4161,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4196,10 +4172,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4400,7 +4376,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4477,10 +4453,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4488,10 +4464,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4646,10 +4622,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4657,10 +4633,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4737,7 +4713,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4814,10 +4790,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4825,10 +4801,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -4838,7 +4814,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
@@ -4873,10 +4849,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4884,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4895,7 +4871,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4906,7 +4882,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4917,20 +4893,9 @@
         <v>73</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C7">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8">
         <v>2000</v>
       </c>
     </row>
@@ -4976,10 +4941,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4987,7 +4952,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4998,7 +4963,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -5009,7 +4974,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -5020,7 +4985,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -5031,7 +4996,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -5315,7 +5280,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5326,7 +5291,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5445,7 +5410,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5456,7 +5421,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5526,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5537,7 +5502,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5692,7 +5657,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>101</v>
@@ -5703,7 +5668,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6252,7 +6217,7 @@
         <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6804,7 +6769,7 @@
         <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7038,7 +7003,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7071,7 +7036,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7082,7 +7047,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -7131,7 +7096,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7164,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7175,7 +7140,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7223,7 +7188,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>97</v>
@@ -7256,7 +7221,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7267,7 +7232,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7315,7 +7280,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>98</v>
@@ -7348,7 +7313,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7359,7 +7324,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7406,7 +7371,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>96</v>
@@ -7439,7 +7404,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7450,7 +7415,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7498,7 +7463,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>99</v>
@@ -7531,7 +7496,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7542,7 +7507,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7589,7 +7554,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7611,7 +7576,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7622,7 +7587,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7669,7 +7634,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7691,7 +7656,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7702,7 +7667,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7863,7 +7828,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7896,7 +7861,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7907,7 +7872,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7954,7 +7919,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>97</v>
@@ -7987,7 +7952,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7998,7 +7963,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -8328,7 +8293,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8339,7 +8304,7 @@
         <v>118</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8350,7 +8315,7 @@
         <v>119</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{566BEBA2-A368-4205-BEA4-0242B730B967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CB4EBB-35A3-4EAE-89FA-1A2B3BBF82BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="163">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4814,7 +4814,7 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
@@ -4886,17 +4886,6 @@
       </c>
       <c r="C6">
         <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C7">
-        <v>2000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49CB4EBB-35A3-4EAE-89FA-1A2B3BBF82BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F122F83-11E3-43FA-BF53-A5513F200D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="30" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="43" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -549,9 +549,6 @@
     <t>Automation IND</t>
   </si>
   <si>
-    <t>Product Sub Recipient Test Organization</t>
-  </si>
-  <si>
     <t>ProjectPeriodStartDate__c</t>
   </si>
   <si>
@@ -586,6 +583,9 @@
   </si>
   <si>
     <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>Framework Defect Retest</t>
   </si>
 </sst>
 </file>
@@ -776,9 +776,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -816,7 +816,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -922,7 +922,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1064,7 +1064,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1176,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1187,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -2152,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>145</v>
@@ -2163,7 +2163,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>143</v>
@@ -4622,7 +4622,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C13" s="18" t="s">
         <v>145</v>
@@ -4633,7 +4633,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>143</v>
@@ -4849,7 +4849,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
         <v>124</v>
@@ -4860,7 +4860,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4871,7 +4871,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4882,7 +4882,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4930,7 +4930,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
         <v>124</v>
@@ -4941,7 +4941,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4952,7 +4952,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4963,7 +4963,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4974,7 +4974,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4985,7 +4985,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -5269,7 +5269,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5399,7 +5399,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5410,7 +5410,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5480,7 +5480,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5491,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -6757,8 +6757,8 @@
       <c r="B6" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>150</v>
+      <c r="C6" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC2\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F122F83-11E3-43FA-BF53-A5513F200D6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B7E5C8-2D5D-494F-B591-2641746A6A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="43" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1073,10 +1073,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1132,9 +1132,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1246,10 +1246,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1359,10 +1359,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.26953125" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1472,10 +1472,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1585,11 +1585,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1700,10 +1700,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1814,9 +1814,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1836,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>107</v>
@@ -1858,7 +1858,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1891,7 +1891,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1928,7 +1928,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -2008,10 +2008,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" customWidth="1"/>
-    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2178,10 +2178,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2358,9 +2358,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2526,10 +2526,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2695,10 +2695,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2842,9 +2842,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3010,10 +3010,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3178,10 +3178,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3346,10 +3346,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3514,10 +3514,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.7265625" customWidth="1"/>
-    <col min="3" max="3" width="35.26953125" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="35.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3682,10 +3682,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3850,10 +3850,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4018,9 +4018,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4186,9 +4186,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4310,9 +4310,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4478,10 +4478,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.7265625" customWidth="1"/>
-    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4647,9 +4647,9 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4815,10 +4815,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.7265625" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4897,9 +4897,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4999,11 +4999,11 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5114,10 +5114,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5236,10 +5236,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5355,9 +5355,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5436,10 +5436,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5517,9 +5517,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5580,7 +5580,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5671,11 +5671,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5907,11 +5907,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5945,11 +5945,11 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6016,10 +6016,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6074,11 +6074,11 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6133,10 +6133,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6181,10 +6181,10 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6228,11 +6228,11 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6430,15 +6430,15 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
-    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.26953125" customWidth="1"/>
-    <col min="7" max="7" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6629,11 +6629,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6688,11 +6688,11 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6802,10 +6802,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6959,10 +6959,10 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7051,11 +7051,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7143,11 +7143,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.7265625" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
-    <col min="3" max="3" width="29.26953125" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7235,11 +7235,11 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7327,7 +7327,7 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7419,10 +7419,10 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7510,9 +7510,9 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7590,7 +7590,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7670,7 +7670,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7784,7 +7784,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7875,7 +7875,7 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7966,10 +7966,10 @@
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" customWidth="1"/>
-    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8080,9 +8080,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8193,7 +8193,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A058B24C-ECE4-4154-B985-11F85C7FD554}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8202,10 +8202,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B7E5C8-2D5D-494F-B591-2641746A6A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC80CAD7-11CC-44E9-AC13-B13B5A304D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="43" activeTab="46" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -20,61 +20,60 @@
     <sheet name="Payment_Request_Wt_Frequency" sheetId="42" r:id="rId5"/>
     <sheet name="Grant_Creation" sheetId="10" r:id="rId6"/>
     <sheet name="Grant_CreationDate" sheetId="44" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="47" r:id="rId8"/>
-    <sheet name="QAorgGrantFields" sheetId="52" r:id="rId9"/>
-    <sheet name="GrantFields1" sheetId="40" r:id="rId10"/>
-    <sheet name="GrantFieldsIndUser" sheetId="61" r:id="rId11"/>
-    <sheet name="GrantFieldsIndUser1" sheetId="63" r:id="rId12"/>
-    <sheet name="GrantsBulksRecords" sheetId="51" r:id="rId13"/>
-    <sheet name="GrantFields3" sheetId="43" r:id="rId14"/>
-    <sheet name="GrantFields2" sheetId="41" r:id="rId15"/>
-    <sheet name="Grant_Create_less_date" sheetId="39" r:id="rId16"/>
-    <sheet name="Progress Report Error" sheetId="27" r:id="rId17"/>
-    <sheet name="Grant_Edition" sheetId="11" r:id="rId18"/>
-    <sheet name="Edit3" sheetId="46" r:id="rId19"/>
-    <sheet name="Grant_Edition2" sheetId="45" r:id="rId20"/>
-    <sheet name="Grant_Ed_Advance_No" sheetId="50" r:id="rId21"/>
-    <sheet name="QAorgGrant_Edition1" sheetId="53" r:id="rId22"/>
-    <sheet name="Grant_Edition_By_Applicant" sheetId="54" r:id="rId23"/>
-    <sheet name="Grant_Edition_ByApp_Focus_No" sheetId="58" r:id="rId24"/>
-    <sheet name="Grant_Edition_By_App_Focus_Yes" sheetId="56" r:id="rId25"/>
-    <sheet name="Grant_Edition_By_App_Focus_Yes2" sheetId="62" r:id="rId26"/>
-    <sheet name="Grant_Edition_Directed" sheetId="57" r:id="rId27"/>
-    <sheet name="Grant_Ed_Directed_Risk_Yes" sheetId="64" r:id="rId28"/>
-    <sheet name="Grant_Edition_Directed_Focus_No" sheetId="59" r:id="rId29"/>
-    <sheet name="Grant_Advance_Yes" sheetId="55" r:id="rId30"/>
-    <sheet name="Grant_Edition1" sheetId="30" r:id="rId31"/>
-    <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId32"/>
-    <sheet name="Edition" sheetId="1" r:id="rId33"/>
-    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId34"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
-    <sheet name="KPI" sheetId="18" r:id="rId46"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
-    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
+    <sheet name="QAorgGrantFields" sheetId="52" r:id="rId8"/>
+    <sheet name="GrantFields1" sheetId="40" r:id="rId9"/>
+    <sheet name="GrantFieldsIndUser" sheetId="61" r:id="rId10"/>
+    <sheet name="GrantFieldsIndUser1" sheetId="63" r:id="rId11"/>
+    <sheet name="GrantsBulksRecords" sheetId="51" r:id="rId12"/>
+    <sheet name="GrantFields3" sheetId="43" r:id="rId13"/>
+    <sheet name="GrantFields2" sheetId="41" r:id="rId14"/>
+    <sheet name="Grant_Create_less_date" sheetId="39" r:id="rId15"/>
+    <sheet name="Progress Report Error" sheetId="27" r:id="rId16"/>
+    <sheet name="Grant_Edition" sheetId="11" r:id="rId17"/>
+    <sheet name="Edit3" sheetId="46" r:id="rId18"/>
+    <sheet name="Grant_Edition2" sheetId="45" r:id="rId19"/>
+    <sheet name="Grant_Ed_Advance_No" sheetId="50" r:id="rId20"/>
+    <sheet name="QAorgGrant_Edition1" sheetId="53" r:id="rId21"/>
+    <sheet name="Grant_Edition_By_Applicant" sheetId="54" r:id="rId22"/>
+    <sheet name="Grant_Edition_ByApp_Focus_No" sheetId="58" r:id="rId23"/>
+    <sheet name="Grant_Edition_By_App_Focus_Yes" sheetId="56" r:id="rId24"/>
+    <sheet name="Grant_Edition_By_App_Focus_Yes2" sheetId="62" r:id="rId25"/>
+    <sheet name="Grant_Edition_Directed" sheetId="57" r:id="rId26"/>
+    <sheet name="Grant_Ed_Directed_Risk_Yes" sheetId="64" r:id="rId27"/>
+    <sheet name="Grant_Edition_Directed_Focus_No" sheetId="59" r:id="rId28"/>
+    <sheet name="Grant_Advance_Yes" sheetId="55" r:id="rId29"/>
+    <sheet name="Grant_Edition1" sheetId="30" r:id="rId30"/>
+    <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId31"/>
+    <sheet name="Edition" sheetId="1" r:id="rId32"/>
+    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId33"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId34"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId35"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId36"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId37"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId38"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId39"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId40"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId41"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId42"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId43"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId44"/>
+    <sheet name="KPI" sheetId="18" r:id="rId45"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId46"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId47"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId48"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId49"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId50"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId51"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId52"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId53"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId54"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId55"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId56"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId57"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId58"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId59"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId60"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId61"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -378,15 +377,9 @@
     <t>Automation Permanent Internal Program</t>
   </si>
   <si>
-    <t>fieldMasterKPI__c</t>
-  </si>
-  <si>
     <t>Automation Permanent KPI for Regression2</t>
   </si>
   <si>
-    <t>fieldTarget__c</t>
-  </si>
-  <si>
     <t>Annually</t>
   </si>
   <si>
@@ -586,6 +579,12 @@
   </si>
   <si>
     <t>Framework Defect Retest</t>
+  </si>
+  <si>
+    <t>MasterKPI__c</t>
+  </si>
+  <si>
+    <t>Target__c</t>
   </si>
 </sst>
 </file>
@@ -1073,10 +1072,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1098,7 +1097,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1130,12 +1129,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1154,10 +1153,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1176,7 +1175,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1187,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1209,7 +1208,233 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="36.54296875" customWidth="1"/>
+    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1220,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1230,11 +1455,125 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="9">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1243,13 +1582,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1268,10 +1608,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1290,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1301,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1323,10 +1663,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1334,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1344,8 +1684,8 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>119</v>
+      <c r="B9" t="s">
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -1356,467 +1696,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="36.5546875" customWidth="1"/>
-    <col min="3" max="3" width="39.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1839,7 +1724,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1858,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1869,7 +1754,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1891,7 +1776,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1925,10 +1810,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1953,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1983,7 +1868,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1994,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -2005,13 +1890,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2152,10 +2037,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2163,10 +2048,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2175,13 +2060,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2322,7 +2207,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2333,10 +2218,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2344,10 +2229,179 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C15" s="18" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="18" t="s">
         <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2358,9 +2412,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2501,10 +2555,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2512,10 +2566,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2524,13 +2578,13 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2640,7 +2694,7 @@
         <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2651,7 +2705,7 @@
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2663,28 +2717,6 @@
       </c>
       <c r="C12" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2693,13 +2725,12 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2717,8 +2748,8 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>74</v>
+      <c r="B2" s="14" t="s">
+        <v>127</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2728,8 +2759,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>75</v>
+      <c r="B3" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2739,8 +2770,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
-        <v>76</v>
+      <c r="B4" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2750,8 +2781,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>77</v>
+      <c r="B5" s="14" t="s">
+        <v>130</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2761,19 +2792,19 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>78</v>
+      <c r="B6" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
-        <v>79</v>
+      <c r="B7" s="14" t="s">
+        <v>132</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2783,8 +2814,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>80</v>
+      <c r="B8" s="14" t="s">
+        <v>133</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2794,8 +2825,8 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
-        <v>81</v>
+      <c r="B9" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2805,8 +2836,8 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
-        <v>82</v>
+      <c r="B10" s="14" t="s">
+        <v>135</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2816,8 +2847,8 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" t="s">
-        <v>83</v>
+      <c r="B11" s="14" t="s">
+        <v>136</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2827,11 +2858,33 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" t="s">
-        <v>86</v>
+      <c r="B12" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2840,12 +2893,12 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2863,8 +2916,8 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>129</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2874,8 +2927,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>130</v>
+      <c r="B3" t="s">
+        <v>75</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2885,8 +2938,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>131</v>
+      <c r="B4" t="s">
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2896,8 +2949,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>132</v>
+      <c r="B5" t="s">
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2908,18 +2961,18 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>134</v>
+      <c r="B7" t="s">
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2929,8 +2982,8 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>135</v>
+      <c r="B8" t="s">
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2940,8 +2993,8 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>136</v>
+      <c r="B9" t="s">
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2951,8 +3004,8 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>137</v>
+      <c r="B10" t="s">
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2962,8 +3015,8 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>138</v>
+      <c r="B11" t="s">
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2973,8 +3026,8 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>139</v>
+      <c r="B12" t="s">
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2984,22 +3037,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>141</v>
+      <c r="B13" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>143</v>
+      <c r="B14" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3008,12 +3061,12 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3076,7 +3129,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3145,7 +3198,7 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3153,10 +3206,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3164,10 +3217,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -3176,12 +3229,12 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3244,7 +3297,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3313,7 +3366,7 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3321,10 +3374,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3332,10 +3385,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>147</v>
+        <v>151</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3344,12 +3397,12 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3412,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3426,7 +3479,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3489,10 +3542,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3500,10 +3553,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3512,12 +3565,12 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.77734375" customWidth="1"/>
-    <col min="3" max="3" width="35.21875" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3580,7 +3633,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3594,7 +3647,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -3657,10 +3710,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>146</v>
+        <v>150</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3668,10 +3721,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3680,12 +3733,12 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3748,7 +3801,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>30</v>
@@ -3806,7 +3859,7 @@
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3817,7 +3870,7 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -3825,10 +3878,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3836,10 +3889,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3848,12 +3901,12 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3916,10 +3969,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -3974,7 +4027,7 @@
         <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -3993,10 +4046,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4004,10 +4057,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4016,12 +4069,12 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4084,7 +4137,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -4161,10 +4214,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>141</v>
+        <v>150</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4172,10 +4225,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>143</v>
+        <v>151</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4186,9 +4239,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4208,10 +4261,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4230,7 +4283,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4241,7 +4294,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4263,7 +4316,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -4308,12 +4361,13 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4376,10 +4430,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4445,7 +4499,7 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4453,10 +4507,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4464,10 +4518,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4476,13 +4530,12 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.77734375" customWidth="1"/>
-    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4548,7 +4601,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4614,7 +4667,7 @@
         <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -4622,10 +4675,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4633,10 +4686,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4645,180 +4698,12 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>143</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4849,10 +4734,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4860,7 +4745,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4871,7 +4756,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4882,7 +4767,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4894,12 +4779,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4930,10 +4815,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4941,7 +4826,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4952,7 +4837,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4963,7 +4848,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4974,7 +4859,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4985,7 +4870,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4996,14 +4881,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5033,7 +4918,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5044,7 +4929,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5066,7 +4951,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5102,7 +4987,129 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" s="6"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5112,12 +5119,12 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5146,8 +5153,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>116</v>
+      <c r="B3" t="s">
+        <v>148</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5157,8 +5164,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>117</v>
+      <c r="B4" t="s">
+        <v>149</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5180,7 +5187,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5216,15 +5223,174 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="C10" s="6"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -5233,13 +5399,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5257,11 +5423,11 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>66</v>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5269,10 +5435,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5280,10 +5446,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5291,21 +5457,21 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>69</v>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5313,213 +5479,23 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" t="s">
-        <v>100</v>
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5542,7 +5518,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5578,104 +5554,13 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5904,14 +5789,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5942,14 +5827,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6013,13 +5898,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6041,7 +5926,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6052,7 +5937,66 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6072,13 +6016,12 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6096,77 +6039,19 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>110</v>
+      <c r="B2" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6178,13 +6063,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6203,10 +6088,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6214,10 +6099,212 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -6226,200 +6313,197 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.1796875" customWidth="1"/>
+    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>54</v>
+      </c>
+      <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="E8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="E16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="5:5">
+      <c r="E18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="5:5">
+      <c r="E19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="5:5">
+      <c r="E20" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="5:5">
+      <c r="E21" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -6428,197 +6512,112 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="E10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="E11" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="E15" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="E16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5">
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="5:5">
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="5:5">
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5">
-      <c r="E20" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="5:5">
-      <c r="E21" t="s">
-        <v>50</v>
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6629,11 +6628,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.77734375" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6655,7 +6654,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6686,23 +6685,22 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.21875" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -6711,10 +6709,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6722,10 +6720,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6733,10 +6731,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6744,21 +6742,21 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>102</v>
+      <c r="B6" t="s">
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>162</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6766,10 +6764,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6777,21 +6775,65 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
+      <c r="B9" t="s">
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6800,12 +6842,12 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6823,11 +6865,11 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>74</v>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6835,10 +6877,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
+        <v>121</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6846,10 +6888,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6857,10 +6899,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6868,10 +6910,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>158</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6879,164 +6921,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -7048,14 +6933,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.77734375" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" customWidth="1"/>
-    <col min="3" max="3" width="49.77734375" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" customWidth="1"/>
+    <col min="3" max="3" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7077,7 +6962,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7085,10 +6970,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7118,7 +7003,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7129,10 +7014,102 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>3700</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -7141,13 +7118,13 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="29.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7169,7 +7146,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7177,10 +7154,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7210,7 +7187,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7221,7 +7198,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7233,101 +7210,9 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="27.77734375" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7352,7 +7237,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7360,10 +7245,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7393,7 +7278,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7404,7 +7289,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7416,13 +7301,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7444,7 +7329,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7452,10 +7337,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7485,7 +7370,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7496,9 +7381,89 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6">
         <v>365</v>
       </c>
     </row>
@@ -7508,89 +7473,9 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7615,7 +7500,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7623,7 +7508,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7645,7 +7530,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7656,10 +7541,101 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C6">
         <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7670,7 +7646,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7692,10 +7668,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7714,7 +7690,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7725,7 +7701,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7747,7 +7723,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7769,7 +7745,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -7782,100 +7758,9 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7900,7 +7785,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7908,10 +7793,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7941,7 +7826,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7952,7 +7837,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7963,13 +7848,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7989,10 +7874,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8011,7 +7896,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8022,7 +7907,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8044,7 +7929,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8080,9 +7965,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8102,10 +7987,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8124,7 +8009,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8135,7 +8020,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8157,7 +8042,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8191,21 +8076,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A058B24C-ECE4-4154-B985-11F85C7FD554}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8224,10 +8100,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8246,7 +8122,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8257,7 +8133,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8282,7 +8158,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8290,10 +8166,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8301,10 +8177,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -8314,4 +8190,118 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC80CAD7-11CC-44E9-AC13-B13B5A304D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA693A29-1FD9-457E-8C21-EDF910F52EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="43" activeTab="46" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA693A29-1FD9-457E-8C21-EDF910F52EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7968E-10D2-4EF5-A461-623921A2456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="20" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7968E-10D2-4EF5-A461-623921A2456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489B91EC-B879-4CB8-8F7C-63FF2FF30848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="20" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="59" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="143">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -371,9 +371,6 @@
     <t>Monthly</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>Automation Permanent Internal Program</t>
   </si>
   <si>
@@ -440,30 +437,12 @@
     <t>fieldProjectTitle__c</t>
   </si>
   <si>
-    <t>fieldProjectPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldProjectPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>fieldProgram__c</t>
   </si>
   <si>
-    <t>fieldExternalOrganization__c</t>
-  </si>
-  <si>
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldFrequency__c</t>
-  </si>
-  <si>
     <t>751  August Lane1</t>
   </si>
   <si>
@@ -479,46 +458,7 @@
     <t>Department of Health</t>
   </si>
   <si>
-    <t>fieldIsMatchRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGranteeMatch__c</t>
-  </si>
-  <si>
-    <t>fieldLaverageAllowed__c</t>
-  </si>
-  <si>
-    <t>fieldIsProgramIncomeAnticipated__c</t>
-  </si>
-  <si>
-    <t>fieldIsAdvancePermitted__c</t>
-  </si>
-  <si>
-    <t>fieldIsBuildUpFunctionality__c</t>
-  </si>
-  <si>
-    <t>fieldIsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldKPIsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldAreExpensesBuildIUpLevel__c</t>
-  </si>
-  <si>
-    <t>fieldRiskAssessmentRequired__c</t>
-  </si>
-  <si>
-    <t>fieldFocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGrantType__c</t>
-  </si>
-  <si>
     <t>Directed</t>
-  </si>
-  <si>
-    <t>fieldAllocationLevel__c</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1097,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1153,10 +1093,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1175,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1186,7 +1126,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1208,10 +1148,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1222,7 +1162,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1266,10 +1206,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1288,7 +1228,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1299,7 +1239,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1321,10 +1261,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1332,10 +1272,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1346,7 +1286,7 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1379,10 +1319,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1401,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1412,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1434,7 +1374,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1445,10 +1385,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1493,10 +1433,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1515,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1526,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1548,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>69</v>
@@ -1562,7 +1502,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1573,7 +1513,7 @@
         <v>71</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1611,7 +1551,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1630,7 +1570,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1641,7 +1581,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1663,7 +1603,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1677,7 +1617,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1724,7 +1664,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1743,7 +1683,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1754,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1776,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1790,7 +1730,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1838,7 +1778,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1868,7 +1808,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1879,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -2037,10 +1977,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2048,10 +1988,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2207,7 +2147,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2218,10 +2158,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2229,10 +2169,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2387,10 +2327,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2398,10 +2338,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2555,10 +2495,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2566,10 +2506,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2749,7 +2689,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2760,7 +2700,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2771,7 +2711,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2782,7 +2722,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2793,7 +2733,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2804,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2815,7 +2755,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2826,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2837,7 +2777,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2848,7 +2788,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2859,7 +2799,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2870,10 +2810,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2881,10 +2821,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3038,10 +2978,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3049,10 +2989,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3206,10 +3146,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3217,10 +3157,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3374,10 +3314,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3385,10 +3325,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3542,10 +3482,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3553,10 +3493,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3710,10 +3650,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3721,10 +3661,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3878,10 +3818,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3889,10 +3829,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4046,10 +3986,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4057,10 +3997,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4214,10 +4154,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4225,10 +4165,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4261,10 +4201,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4283,7 +4223,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4294,7 +4234,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4316,7 +4256,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -4330,7 +4270,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4507,10 +4447,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4518,10 +4458,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4675,10 +4615,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4686,10 +4626,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -4734,10 +4674,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4745,7 +4685,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4756,7 +4696,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4767,7 +4707,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4815,10 +4755,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4826,7 +4766,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4837,7 +4777,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4848,7 +4788,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4859,7 +4799,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4870,7 +4810,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4918,7 +4858,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4929,7 +4869,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -4951,7 +4891,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -4965,7 +4905,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4987,7 +4927,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5032,7 +4972,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5043,7 +4983,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5065,7 +5005,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5079,7 +5019,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5101,7 +5041,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5109,7 +5049,7 @@
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5154,7 +5094,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5165,7 +5105,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5187,7 +5127,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5201,7 +5141,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5223,12 +5163,12 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5265,7 +5205,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5284,7 +5224,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5295,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5346,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5365,7 +5305,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5376,7 +5316,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5427,7 +5367,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5468,10 +5408,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5479,7 +5419,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5518,7 +5458,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5926,7 +5866,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5937,7 +5877,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5985,7 +5925,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5996,7 +5936,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6040,10 +5980,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6051,7 +5991,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6088,10 +6028,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6099,7 +6039,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6548,7 +6488,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6559,7 +6499,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6581,10 +6521,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6595,7 +6535,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6617,7 +6557,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6654,7 +6594,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6869,7 +6809,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6877,10 +6817,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6910,7 +6850,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6921,7 +6861,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6962,7 +6902,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6970,10 +6910,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7003,7 +6943,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7014,7 +6954,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7054,7 +6994,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7062,10 +7002,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7095,7 +7035,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7106,7 +7046,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7146,7 +7086,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7154,10 +7094,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7187,7 +7127,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7198,7 +7138,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7237,7 +7177,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7245,10 +7185,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7278,7 +7218,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7289,7 +7229,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7329,7 +7269,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7337,10 +7277,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7370,7 +7310,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7381,7 +7321,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7420,7 +7360,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7428,7 +7368,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7450,7 +7390,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7461,7 +7401,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7500,7 +7440,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7508,7 +7448,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7530,7 +7470,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7541,7 +7481,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7580,7 +7520,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7588,7 +7528,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7621,7 +7561,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7632,7 +7572,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7668,10 +7608,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7690,7 +7630,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7701,7 +7641,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7723,7 +7663,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7737,7 +7677,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7745,7 +7685,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -7785,7 +7725,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7793,10 +7733,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7826,7 +7766,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7837,7 +7777,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7874,10 +7814,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7896,7 +7836,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7907,7 +7847,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7929,7 +7869,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7943,7 +7883,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7987,10 +7927,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8009,7 +7949,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8020,7 +7960,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8042,7 +7982,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8056,7 +7996,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8100,10 +8040,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8122,7 +8062,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8133,7 +8073,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8155,10 +8095,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8166,10 +8106,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8177,10 +8117,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -8220,7 +8160,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8239,7 +8179,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8250,7 +8190,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8272,7 +8212,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8286,7 +8226,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7968E-10D2-4EF5-A461-623921A2456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE04032-AC44-481C-8BB5-E4B47E34FBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="20" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="59" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="148">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -437,9 +437,6 @@
     <t xml:space="preserve">Automation Runtime Payment Request </t>
   </si>
   <si>
-    <t>fieldProjectTitle__c</t>
-  </si>
-  <si>
     <t>fieldProjectPeriodStartDate__c</t>
   </si>
   <si>
@@ -461,9 +458,6 @@
     <t>fieldCalReportingEndDate__c</t>
   </si>
   <si>
-    <t>fieldFrequency__c</t>
-  </si>
-  <si>
     <t>751  August Lane1</t>
   </si>
   <si>
@@ -479,46 +473,7 @@
     <t>Department of Health</t>
   </si>
   <si>
-    <t>fieldIsMatchRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGranteeMatch__c</t>
-  </si>
-  <si>
-    <t>fieldLaverageAllowed__c</t>
-  </si>
-  <si>
-    <t>fieldIsProgramIncomeAnticipated__c</t>
-  </si>
-  <si>
-    <t>fieldIsAdvancePermitted__c</t>
-  </si>
-  <si>
-    <t>fieldIsBuildUpFunctionality__c</t>
-  </si>
-  <si>
-    <t>fieldIsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldKPIsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldAreExpensesBuildIUpLevel__c</t>
-  </si>
-  <si>
-    <t>fieldRiskAssessmentRequired__c</t>
-  </si>
-  <si>
-    <t>fieldFocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGrantType__c</t>
-  </si>
-  <si>
     <t>Directed</t>
-  </si>
-  <si>
-    <t>fieldAllocationLevel__c</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1072,10 +1027,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1131,10 +1086,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1153,7 +1108,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -1175,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1186,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1211,7 +1166,7 @@
         <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1244,10 +1199,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1266,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -1288,7 +1243,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1299,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1324,7 +1279,7 @@
         <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1332,7 +1287,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1357,10 +1312,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1379,10 +1334,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1401,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1412,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1445,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>
@@ -1470,11 +1425,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1493,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>103</v>
@@ -1515,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1526,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1585,10 +1540,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1630,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1641,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1699,9 +1654,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1743,7 +1698,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1754,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1813,7 +1768,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1868,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1879,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1893,10 +1848,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2037,10 +1992,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2048,10 +2003,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2063,10 +2018,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2218,10 +2173,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2229,10 +2184,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2243,10 +2198,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2387,10 +2342,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2398,10 +2353,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2412,9 +2367,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2555,10 +2510,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2566,10 +2521,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2580,10 +2535,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2727,9 +2682,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2749,7 +2704,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2760,7 +2715,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2771,7 +2726,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2782,7 +2737,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2793,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2804,7 +2759,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2815,7 +2770,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2826,7 +2781,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2837,7 +2792,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2848,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2859,7 +2814,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2870,10 +2825,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2881,10 +2836,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2895,10 +2850,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3038,10 +2993,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3049,10 +3004,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3063,10 +3018,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3206,10 +3161,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3217,10 +3172,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -3231,10 +3186,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3374,10 +3329,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3385,10 +3340,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3399,10 +3354,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3542,10 +3497,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3553,10 +3508,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -3567,10 +3522,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3710,10 +3665,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3721,10 +3676,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3735,10 +3690,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3878,10 +3833,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3889,10 +3844,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3903,9 +3858,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4046,10 +4001,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4057,10 +4012,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4071,9 +4026,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4214,10 +4169,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4225,10 +4180,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4239,9 +4194,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4261,7 +4216,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
@@ -4283,7 +4238,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4294,7 +4249,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4363,10 +4318,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4507,10 +4462,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4518,10 +4473,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4532,9 +4487,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4675,10 +4630,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4686,10 +4641,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -4700,10 +4655,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4734,10 +4689,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4745,7 +4700,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4756,7 +4711,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4767,7 +4722,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4782,9 +4737,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4815,10 +4770,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4826,7 +4781,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4837,7 +4792,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4848,7 +4803,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4859,7 +4814,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4870,7 +4825,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4884,11 +4839,11 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4918,7 +4873,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4929,7 +4884,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -4999,10 +4954,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5032,7 +4987,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5043,7 +4998,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5121,10 +5076,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5154,7 +5109,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5165,7 +5120,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5240,9 +5195,9 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5284,7 +5239,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5295,7 +5250,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5321,10 +5276,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5365,7 +5320,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5376,7 +5331,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5402,7 +5357,7 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5468,7 +5423,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>99</v>
@@ -5479,7 +5434,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5493,9 +5448,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5556,11 +5511,11 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5792,11 +5747,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5830,11 +5785,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5901,10 +5856,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5937,7 +5892,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5959,11 +5914,11 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5996,7 +5951,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6018,10 +5973,10 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6040,7 +5995,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>93</v>
@@ -6051,7 +6006,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6066,10 +6021,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6088,10 +6043,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6099,7 +6054,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6113,11 +6068,11 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6315,15 +6270,15 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6514,11 +6469,11 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6548,7 +6503,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6559,7 +6514,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6584,7 +6539,7 @@
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6628,11 +6583,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6687,10 +6642,10 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6844,10 +6799,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6877,7 +6832,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>94</v>
@@ -6910,7 +6865,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6921,7 +6876,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6936,11 +6891,11 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6970,7 +6925,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>94</v>
@@ -7003,7 +6958,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7014,7 +6969,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7028,11 +6983,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7062,7 +7017,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>95</v>
@@ -7095,7 +7050,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7106,7 +7061,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7120,11 +7075,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7154,7 +7109,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7187,7 +7142,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7198,7 +7153,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7212,7 +7167,7 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7245,7 +7200,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>94</v>
@@ -7278,7 +7233,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7289,7 +7244,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7304,10 +7259,10 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7337,7 +7292,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>97</v>
@@ -7370,7 +7325,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7381,7 +7336,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7395,9 +7350,9 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7428,7 +7383,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7450,7 +7405,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7461,7 +7416,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7475,7 +7430,7 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7508,7 +7463,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7530,7 +7485,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7541,7 +7496,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7555,7 +7510,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7588,7 +7543,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7621,7 +7576,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7632,7 +7587,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7646,7 +7601,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7668,7 +7623,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>105</v>
@@ -7690,7 +7645,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7701,7 +7656,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7745,7 +7700,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -7760,7 +7715,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7793,7 +7748,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>95</v>
@@ -7826,7 +7781,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7837,7 +7792,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7851,10 +7806,10 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7874,7 +7829,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
@@ -7896,7 +7851,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7907,7 +7862,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7965,9 +7920,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7987,7 +7942,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
@@ -8009,7 +7964,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8020,7 +7975,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8078,10 +8033,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8100,7 +8055,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -8122,7 +8077,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8133,13 +8088,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8150,7 +8105,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8158,7 +8113,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8166,10 +8121,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8177,10 +8132,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8195,9 +8150,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8239,7 +8194,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8250,7 +8205,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="C5">
         <v>3650</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489B91EC-B879-4CB8-8F7C-63FF2FF30848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F80991-0BDB-4F16-AF21-1C582B931EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="59" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F80991-0BDB-4F16-AF21-1C582B931EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7ABB66-DC8A-4621-987E-B54971038AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="31" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -46,34 +46,35 @@
     <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId31"/>
     <sheet name="Edition" sheetId="1" r:id="rId32"/>
     <sheet name="Edition_StandAlone" sheetId="9" r:id="rId33"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId34"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId35"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId36"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId37"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId38"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId39"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId40"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId41"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId42"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId43"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId44"/>
-    <sheet name="KPI" sheetId="18" r:id="rId45"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId46"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId47"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId48"/>
-    <sheet name="Grant_Creation5" sheetId="65" r:id="rId49"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId50"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId51"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId52"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId53"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId54"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId55"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId56"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId57"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId58"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId59"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId60"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId61"/>
+    <sheet name="Edition_ByAppFocusYes" sheetId="66" r:id="rId34"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
+    <sheet name="KPI" sheetId="18" r:id="rId46"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="143">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4822,6 +4823,97 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418F5EE7-2052-4ACD-A8F6-3010E62CE6D2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="26.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -4936,7 +5028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5058,7 +5150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5177,7 +5269,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5258,7 +5350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5336,97 +5428,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5494,6 +5495,97 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5729,7 +5821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5767,7 +5859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5838,7 +5930,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5896,7 +5988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -5955,7 +6047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6003,7 +6095,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -6050,7 +6142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6252,7 +6344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6444,120 +6536,6 @@
     <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6625,6 +6603,120 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6781,7 +6873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6873,7 +6965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -6965,7 +7057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7057,7 +7149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7149,7 +7241,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7241,7 +7333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7332,7 +7424,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7412,7 +7504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7485,97 +7577,6 @@
       </c>
       <c r="C6">
         <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7698,6 +7699,97 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
@@ -7788,7 +7880,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE04032-AC44-481C-8BB5-E4B47E34FBA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCC6A98-04C9-4023-A479-1EF6CAF86DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="59" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="144">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -371,9 +371,6 @@
     <t>Monthly</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>Automation Permanent Internal Program</t>
   </si>
   <si>
@@ -437,16 +434,7 @@
     <t xml:space="preserve">Automation Runtime Payment Request </t>
   </si>
   <si>
-    <t>fieldProjectPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldProjectPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>fieldProgram__c</t>
-  </si>
-  <si>
-    <t>fieldExternalOrganization__c</t>
   </si>
   <si>
     <t>Automation SPI3</t>
@@ -546,7 +534,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,12 +579,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF202124"/>
       <name val="Consolas"/>
@@ -627,6 +609,25 @@
       <sz val="9.8000000000000007"/>
       <color rgb="FF297BDE"/>
       <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -670,9 +671,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -701,16 +702,21 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1052,7 +1058,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1111,7 +1117,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1129,8 +1135,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1140,8 +1146,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1163,10 +1169,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1177,14 +1183,14 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
@@ -1224,7 +1230,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1242,8 +1248,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1253,8 +1259,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1276,10 +1282,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1287,21 +1293,21 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1343,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1355,8 +1361,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1366,8 +1372,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1389,7 +1395,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1400,17 +1406,17 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
@@ -1451,7 +1457,7 @@
         <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1469,8 +1475,8 @@
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1480,8 +1486,8 @@
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1503,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>69</v>
@@ -1517,7 +1523,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1528,7 +1534,7 @@
         <v>71</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1566,7 +1572,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1584,8 +1590,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1595,8 +1601,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1618,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1632,7 +1638,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1654,9 +1660,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="21" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1664,7 +1670,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1675,18 +1681,18 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="20" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="21" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
@@ -1697,8 +1703,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="22" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1708,8 +1714,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="22" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1719,7 +1725,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="21" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
@@ -1730,8 +1736,8 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>100</v>
+      <c r="B7" s="20" t="s">
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1741,18 +1747,18 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="21" t="s">
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="21" t="s">
         <v>71</v>
       </c>
       <c r="C9" t="s">
@@ -1793,7 +1799,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1823,7 +1829,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1834,7 +1840,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1914,7 +1920,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -1991,22 +1997,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2162,7 +2168,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2172,22 +2178,22 @@
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>128</v>
+      <c r="B14" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>126</v>
+      <c r="B15" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2341,22 +2347,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2509,22 +2515,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2703,7 +2709,7 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
@@ -2714,7 +2720,7 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C3">
@@ -2725,7 +2731,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
@@ -2736,7 +2742,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>77</v>
       </c>
       <c r="C5" t="s">
@@ -2747,7 +2753,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -2758,7 +2764,7 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
@@ -2769,7 +2775,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>80</v>
       </c>
       <c r="C8" t="s">
@@ -2780,7 +2786,7 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>81</v>
       </c>
       <c r="C9" t="s">
@@ -2791,7 +2797,7 @@
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>82</v>
       </c>
       <c r="C10" t="s">
@@ -2802,7 +2808,7 @@
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C11" t="s">
@@ -2813,7 +2819,7 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>86</v>
       </c>
       <c r="C12" t="s">
@@ -2824,22 +2830,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>125</v>
+      <c r="B13" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>126</v>
+      <c r="B14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2915,7 +2921,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -2992,22 +2998,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>129</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>130</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3083,7 +3089,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -3160,22 +3166,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>129</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>130</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -3251,7 +3257,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -3328,22 +3334,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>129</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>131</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3419,7 +3425,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -3496,22 +3502,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>129</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>131</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3593,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -3664,22 +3670,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>125</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3755,7 +3761,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -3832,22 +3838,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>125</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3923,7 +3929,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -4000,22 +4006,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>125</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4091,7 +4097,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -4168,22 +4174,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4219,7 +4225,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4237,8 +4243,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4248,8 +4254,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4271,7 +4277,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -4285,7 +4291,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4384,7 +4390,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -4461,22 +4467,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4552,7 +4558,7 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>78</v>
       </c>
       <c r="C6" t="s">
@@ -4629,22 +4635,22 @@
       <c r="A13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>128</v>
+      <c r="B13" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>126</v>
+      <c r="B14" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -4689,10 +4695,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4700,7 +4706,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4711,7 +4717,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4721,8 +4727,8 @@
       <c r="A6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>140</v>
+      <c r="B6" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4770,10 +4776,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4781,7 +4787,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4792,7 +4798,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4803,7 +4809,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4814,7 +4820,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4825,7 +4831,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4872,8 +4878,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>133</v>
+      <c r="B3" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4883,8 +4889,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>134</v>
+      <c r="B4" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -4906,7 +4912,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -4920,7 +4926,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4942,7 +4948,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -4986,8 +4992,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>133</v>
+      <c r="B3" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4997,8 +5003,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>134</v>
+      <c r="B4" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5020,7 +5026,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5034,7 +5040,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5056,7 +5062,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5064,7 +5070,7 @@
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5109,7 +5115,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5120,7 +5126,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5142,7 +5148,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5156,7 +5162,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5178,12 +5184,12 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5220,7 +5226,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5239,7 +5245,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5250,7 +5256,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5301,7 +5307,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5320,7 +5326,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5331,7 +5337,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5382,7 +5388,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5423,10 +5429,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5434,7 +5440,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5473,7 +5479,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5881,7 +5887,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5892,7 +5898,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5940,7 +5946,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5951,7 +5957,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5995,10 +6001,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6006,7 +6012,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6043,10 +6049,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6054,7 +6060,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6503,7 +6509,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6514,7 +6520,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6535,11 +6541,11 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>100</v>
+      <c r="B6" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6550,7 +6556,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6568,11 +6574,11 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6609,7 +6615,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6824,7 +6830,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6835,7 +6841,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6865,7 +6871,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6876,7 +6882,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6917,7 +6923,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6928,7 +6934,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6958,7 +6964,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6969,7 +6975,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7009,7 +7015,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7020,7 +7026,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7050,7 +7056,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7061,7 +7067,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7101,7 +7107,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7112,7 +7118,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7142,7 +7148,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7153,7 +7159,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7192,7 +7198,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7203,7 +7209,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7233,7 +7239,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7244,7 +7250,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7284,7 +7290,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7295,7 +7301,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7325,7 +7331,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7336,7 +7342,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7375,7 +7381,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7405,7 +7411,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7416,7 +7422,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7455,7 +7461,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7485,7 +7491,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7496,7 +7502,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7535,7 +7541,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7576,7 +7582,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7587,7 +7593,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7626,7 +7632,7 @@
         <v>65</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7644,8 +7650,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7655,8 +7661,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7678,7 +7684,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7692,7 +7698,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7740,7 +7746,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7751,7 +7757,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7781,7 +7787,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7792,7 +7798,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7832,7 +7838,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7850,8 +7856,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7861,8 +7867,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7884,7 +7890,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7898,7 +7904,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7945,7 +7951,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7963,8 +7969,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7974,8 +7980,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7997,7 +8003,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8011,7 +8017,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8058,7 +8064,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8076,8 +8082,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>113</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8087,8 +8093,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>114</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8110,10 +8116,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>123</v>
+        <v>99</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8121,21 +8127,21 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>127</v>
+        <v>70</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>124</v>
+      <c r="B9" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -8175,7 +8181,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8193,8 +8199,8 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>133</v>
+      <c r="B4" s="13" t="s">
+        <v>129</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8204,8 +8210,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>134</v>
+      <c r="B5" s="13" t="s">
+        <v>130</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8227,7 +8233,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8241,7 +8247,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7968E-10D2-4EF5-A461-623921A2456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6690F689-D9FE-4401-BFD3-9EF65E458E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="20" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1072,10 +1072,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1131,10 +1131,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1244,10 +1244,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="39.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1357,10 +1357,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1470,11 +1470,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1493,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>103</v>
@@ -1585,10 +1585,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1699,9 +1699,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1813,7 +1813,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1893,10 +1893,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2063,10 +2063,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2243,10 +2243,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2412,9 +2412,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2580,10 +2580,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2727,9 +2727,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2895,10 +2895,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3063,10 +3063,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3231,10 +3231,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3399,10 +3399,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="35.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3567,10 +3567,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3735,10 +3735,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3903,9 +3903,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4071,9 +4071,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4239,9 +4239,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4363,10 +4363,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.77734375" customWidth="1"/>
+    <col min="2" max="2" width="29.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4532,9 +4532,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4700,10 +4700,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4782,9 +4782,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4884,11 +4884,11 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4999,10 +4999,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5121,10 +5121,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5240,9 +5240,9 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5321,10 +5321,10 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5402,7 +5402,7 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5493,9 +5493,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5556,11 +5556,11 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5792,11 +5792,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5830,11 +5830,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5901,10 +5901,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5959,11 +5959,11 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6018,10 +6018,10 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6066,10 +6066,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6113,11 +6113,11 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6315,15 +6315,15 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" customWidth="1"/>
+    <col min="2" max="2" width="9.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.21875" customWidth="1"/>
+    <col min="7" max="7" width="13.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6514,11 +6514,11 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6628,11 +6628,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6687,10 +6687,10 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6844,10 +6844,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6936,11 +6936,11 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="49.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7028,11 +7028,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.77734375" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7120,11 +7120,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7212,7 +7212,7 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7304,10 +7304,10 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7395,9 +7395,9 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7475,7 +7475,7 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7555,7 +7555,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7646,7 +7646,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7760,7 +7760,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7851,10 +7851,10 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7965,9 +7965,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8078,10 +8078,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8195,9 +8195,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCC6A98-04C9-4023-A479-1EF6CAF86DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B282591-FA57-466C-B1A8-AC6F3AB47C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="59" activeTab="60" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="38" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -5519,7 +5519,7 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6690F689-D9FE-4401-BFD3-9EF65E458E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9D3B4B-6988-43B3-8CAC-A210815D01EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1153,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>
@@ -1266,7 +1266,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>103</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B282591-FA57-466C-B1A8-AC6F3AB47C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F172E45-873B-46CE-8368-D2B1B983DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="38" activeTab="40" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="144">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4199,10 +4199,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4302,17 +4302,6 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
         <v>72</v>
       </c>
     </row>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7968E-10D2-4EF5-A461-623921A2456E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42B079E-0CEA-42A5-8F18-85CEE0C79141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="20" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="163">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -591,7 +591,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -674,6 +674,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -717,7 +723,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -756,6 +762,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1072,10 +1079,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1131,10 +1138,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1244,10 +1251,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1357,10 +1364,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1470,11 +1477,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1585,10 +1592,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1699,9 +1706,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1813,7 +1820,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1893,10 +1900,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2063,10 +2070,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2243,10 +2250,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2412,9 +2419,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2580,10 +2587,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2727,9 +2734,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2895,10 +2902,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3063,10 +3070,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3231,10 +3238,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3399,10 +3406,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
-    <col min="3" max="3" width="35.1796875" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+    <col min="3" max="3" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3567,10 +3574,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3735,10 +3742,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3903,9 +3910,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4071,9 +4078,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4239,9 +4246,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4363,10 +4370,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" customWidth="1"/>
-    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4532,9 +4539,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4700,10 +4707,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4782,9 +4789,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4884,11 +4891,11 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4999,10 +5006,10 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5121,10 +5128,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5239,10 +5246,10 @@
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5298,7 +5305,7 @@
         <v>159</v>
       </c>
       <c r="C5">
-        <v>3650</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5310,6 +5317,17 @@
       </c>
       <c r="C6" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5320,11 +5338,11 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5379,7 +5397,7 @@
         <v>159</v>
       </c>
       <c r="C5">
-        <v>3650</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5391,6 +5409,17 @@
       </c>
       <c r="C6" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5402,7 +5431,7 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5493,9 +5522,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5556,11 +5585,11 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5792,11 +5821,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1796875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5830,11 +5859,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5901,10 +5930,10 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5959,11 +5988,11 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6018,10 +6047,10 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6066,10 +6095,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6113,11 +6142,11 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6315,15 +6344,15 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6514,11 +6543,11 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.1796875" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6628,11 +6657,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.81640625" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6687,10 +6716,10 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6844,10 +6873,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6936,11 +6965,11 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
-    <col min="2" max="2" width="32.81640625" customWidth="1"/>
-    <col min="3" max="3" width="49.81640625" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.85546875" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7028,11 +7057,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.81640625" customWidth="1"/>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7120,11 +7149,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27.81640625" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.1796875" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7212,7 +7241,7 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7304,10 +7333,10 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7395,9 +7424,9 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7475,7 +7504,7 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7555,7 +7584,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7646,7 +7675,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7760,7 +7789,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7851,10 +7880,10 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7965,9 +7994,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.453125" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8078,10 +8107,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8139,7 +8168,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" thickBot="1">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8150,7 +8179,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" thickBot="1">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -8195,9 +8224,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F172E45-873B-46CE-8368-D2B1B983DED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9798C1-7F27-4D9F-A9D8-30BA3B75DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42B079E-0CEA-42A5-8F18-85CEE0C79141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2910DE64-7776-4AD3-A993-2E9D13CF8A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="57" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="161">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -453,12 +453,6 @@
   </si>
   <si>
     <t>Automation SPI3</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
   </si>
   <si>
     <t>fieldFrequency__c</t>
@@ -1182,7 +1176,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1193,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1218,7 +1212,7 @@
         <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1295,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1306,7 +1300,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1331,7 +1325,7 @@
         <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1389,7 +1383,7 @@
         <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1408,7 +1402,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1419,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1522,7 +1516,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1533,7 +1527,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1637,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1648,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1750,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1761,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1874,8 +1868,8 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>119</v>
+      <c r="B5" s="20" t="s">
+        <v>156</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1885,8 +1879,8 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>120</v>
+      <c r="B6" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -2044,10 +2038,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2055,10 +2049,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2225,10 +2219,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2236,10 +2230,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2394,10 +2388,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2405,10 +2399,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2562,10 +2556,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2573,10 +2567,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2756,7 +2750,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2767,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2778,7 +2772,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2789,7 +2783,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2800,7 +2794,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2811,7 +2805,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2822,7 +2816,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2833,7 +2827,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2844,7 +2838,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2855,7 +2849,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2866,7 +2860,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2877,10 +2871,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2888,10 +2882,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3045,10 +3039,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3056,10 +3050,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3213,10 +3207,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3224,10 +3218,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3381,10 +3375,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3392,10 +3386,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -3549,10 +3543,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3560,10 +3554,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -3717,10 +3711,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3728,10 +3722,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -3885,10 +3879,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3896,10 +3890,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4053,10 +4047,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4064,10 +4058,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4221,10 +4215,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4232,10 +4226,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4290,7 +4284,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4301,7 +4295,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4514,10 +4508,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4525,10 +4519,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4682,10 +4676,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4693,10 +4687,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -4741,10 +4735,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4752,7 +4746,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4763,7 +4757,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4774,7 +4768,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4822,10 +4816,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4833,7 +4827,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4844,7 +4838,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4855,7 +4849,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4866,7 +4860,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4877,7 +4871,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4925,7 +4919,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4936,7 +4930,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5039,7 +5033,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5050,7 +5044,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5161,7 +5155,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5172,7 +5166,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5291,7 +5285,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5302,7 +5296,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5383,7 +5377,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5394,7 +5388,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5497,7 +5491,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>99</v>
@@ -5508,7 +5502,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6069,7 +6063,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>93</v>
@@ -6080,7 +6074,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6117,10 +6111,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6128,7 +6122,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6613,7 +6607,7 @@
         <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6905,8 +6899,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>94</v>
@@ -6939,7 +6933,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6950,7 +6944,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6998,8 +6992,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>94</v>
@@ -7032,7 +7026,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7043,7 +7037,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7090,8 +7084,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>95</v>
@@ -7124,7 +7118,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7135,7 +7129,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7182,8 +7176,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>96</v>
@@ -7216,7 +7210,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7227,7 +7221,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7274,7 +7268,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>94</v>
@@ -7307,7 +7301,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7318,7 +7312,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7365,8 +7359,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>97</v>
@@ -7399,7 +7393,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7410,7 +7404,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7457,7 +7451,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7479,7 +7473,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7490,7 +7484,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7537,7 +7531,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>121</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7559,7 +7553,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7570,7 +7564,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7616,8 +7610,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>90</v>
@@ -7650,7 +7644,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7661,7 +7655,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7719,7 +7713,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7730,7 +7724,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7821,8 +7815,8 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
-        <v>121</v>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>95</v>
@@ -7855,7 +7849,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7866,7 +7860,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7874,6 +7868,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7925,7 +7920,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7936,7 +7931,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8038,7 +8033,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8049,7 +8044,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8187,7 +8182,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8198,7 +8193,7 @@
         <v>116</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8209,7 +8204,7 @@
         <v>117</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -8268,7 +8263,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8279,7 +8274,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C5">
         <v>3650</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F9D3B4B-6988-43B3-8CAC-A210815D01EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD42D611-2A6F-4F68-BDC0-69E3F0FE2FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1332,7 +1332,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>92</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0D3DAD-A509-4D20-8083-1FC88A79CCAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E68872-20AB-410E-826F-CDF198A8431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="0" windowWidth="20355" windowHeight="10920" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="46" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -23,58 +23,81 @@
     <sheet name="Sheet2" sheetId="47" r:id="rId8"/>
     <sheet name="QAorgGrantFields" sheetId="52" r:id="rId9"/>
     <sheet name="GrantFields1" sheetId="40" r:id="rId10"/>
-    <sheet name="GrantsBulksRecords" sheetId="51" r:id="rId11"/>
-    <sheet name="GrantFields3" sheetId="43" r:id="rId12"/>
-    <sheet name="GrantFields2" sheetId="41" r:id="rId13"/>
-    <sheet name="Grant_Create_less_date" sheetId="39" r:id="rId14"/>
-    <sheet name="Progress Report Error" sheetId="27" r:id="rId15"/>
-    <sheet name="Grant_Edition" sheetId="11" r:id="rId16"/>
-    <sheet name="Edit3" sheetId="46" r:id="rId17"/>
-    <sheet name="Grant_Edition2" sheetId="45" r:id="rId18"/>
-    <sheet name="Grant_Ed_Advance_No" sheetId="50" r:id="rId19"/>
-    <sheet name="QAorgGrant_Edition1" sheetId="53" r:id="rId20"/>
-    <sheet name="Grant_Edition1" sheetId="30" r:id="rId21"/>
-    <sheet name="Edition" sheetId="1" r:id="rId22"/>
-    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId23"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId24"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId25"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId26"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId27"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId28"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId29"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId30"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId31"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId32"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId33"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId34"/>
-    <sheet name="KPI" sheetId="18" r:id="rId35"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId36"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId37"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId38"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId39"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId40"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId41"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId42"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId43"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId44"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId45"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId46"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId47"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId48"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId49"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId50"/>
+    <sheet name="GrantFieldsIndUser" sheetId="61" r:id="rId11"/>
+    <sheet name="GrantFieldsIndUser1" sheetId="63" r:id="rId12"/>
+    <sheet name="GrantsBulksRecords" sheetId="51" r:id="rId13"/>
+    <sheet name="GrantFields3" sheetId="43" r:id="rId14"/>
+    <sheet name="GrantFields2" sheetId="41" r:id="rId15"/>
+    <sheet name="Grant_Create_less_date" sheetId="39" r:id="rId16"/>
+    <sheet name="Progress Report Error" sheetId="27" r:id="rId17"/>
+    <sheet name="Grant_Edition" sheetId="11" r:id="rId18"/>
+    <sheet name="Edit3" sheetId="46" r:id="rId19"/>
+    <sheet name="Grant_Edition2" sheetId="45" r:id="rId20"/>
+    <sheet name="Grant_Ed_Advance_No" sheetId="50" r:id="rId21"/>
+    <sheet name="QAorgGrant_Edition1" sheetId="53" r:id="rId22"/>
+    <sheet name="Grant_Edition_By_Applicant" sheetId="54" r:id="rId23"/>
+    <sheet name="Grant_Edition_ByApp_Focus_No" sheetId="58" r:id="rId24"/>
+    <sheet name="Grant_Edition_By_App_Focus_Yes" sheetId="56" r:id="rId25"/>
+    <sheet name="Grant_Edition_By_App_Focus_Yes2" sheetId="62" r:id="rId26"/>
+    <sheet name="Grant_Edition_Directed" sheetId="57" r:id="rId27"/>
+    <sheet name="Grant_Ed_Directed_Risk_Yes" sheetId="64" r:id="rId28"/>
+    <sheet name="Grant_Edition_Directed_Focus_No" sheetId="59" r:id="rId29"/>
+    <sheet name="Grant_Advance_Yes" sheetId="55" r:id="rId30"/>
+    <sheet name="Grant_Edition1" sheetId="30" r:id="rId31"/>
+    <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId32"/>
+    <sheet name="Edition" sheetId="1" r:id="rId33"/>
+    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId34"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
+    <sheet name="KPI" sheetId="18" r:id="rId46"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="161">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -469,9 +492,6 @@
     <t>fieldCongressionalDistrictName__c</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>fieldZipCode4Extension__c</t>
   </si>
   <si>
@@ -536,13 +556,37 @@
   </si>
   <si>
     <t>PG-T09-0768</t>
+  </si>
+  <si>
+    <t>Competitive</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>By Applicant</t>
+  </si>
+  <si>
+    <t>fieldNewObligation__c</t>
+  </si>
+  <si>
+    <t>fieldTotalCommitment__c</t>
+  </si>
+  <si>
+    <t>By Applicant and Focus Area</t>
+  </si>
+  <si>
+    <t>Automation IND</t>
+  </si>
+  <si>
+    <t>Product Sub Recipient Test Organization</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,6 +656,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -655,7 +712,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -689,6 +746,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1006,13 +1067,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1034,7 +1095,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1045,7 +1106,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1065,13 +1126,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1093,7 +1154,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1104,7 +1165,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1115,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1126,7 +1187,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1137,7 +1198,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1148,7 +1209,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1220,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1177,15 +1238,15 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1257,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1204,10 +1265,10 @@
         <v>115</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1218,7 +1279,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1229,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1240,7 +1301,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1251,18 +1312,18 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1334,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1290,16 +1351,242 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1608,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
@@ -1332,7 +1619,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
@@ -1343,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
@@ -1354,7 +1641,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
@@ -1365,7 +1652,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
@@ -1376,7 +1663,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
@@ -1387,7 +1674,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
@@ -1400,20 +1687,21 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1424,7 +1712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1723,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1446,7 +1734,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1468,7 +1756,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1479,7 +1767,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1490,7 +1778,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1501,7 +1789,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1517,16 +1805,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1548,7 +1836,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1559,7 +1847,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1570,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1581,7 +1869,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1592,7 +1880,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1603,7 +1891,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1614,7 +1902,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1631,16 +1919,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1662,7 +1950,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1673,7 +1961,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1684,7 +1972,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1695,7 +1983,7 @@
         <v>-300</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1711,17 +1999,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,7 +2020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1743,7 +2031,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1754,7 +2042,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1765,7 +2053,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1776,18 +2064,18 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>78</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1798,7 +2086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +2097,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1820,7 +2108,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1831,7 +2119,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1842,7 +2130,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1851,6 +2139,28 @@
       </c>
       <c r="C12" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1859,17 +2169,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1880,7 +2190,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1891,7 +2201,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1902,7 +2212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1913,7 +2223,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1924,7 +2234,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1932,10 +2242,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1946,7 +2256,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1957,7 +2267,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -1968,7 +2278,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1979,7 +2289,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -1990,7 +2300,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2001,7 +2311,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2012,297 +2322,26 @@
         <v>15</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2312,14 +2351,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2330,7 +2369,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2341,7 +2380,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2352,7 +2391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2363,7 +2402,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2374,7 +2413,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2382,10 +2421,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2396,7 +2435,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2407,7 +2446,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2418,7 +2457,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2429,7 +2468,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2440,7 +2479,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2449,6 +2488,28 @@
       </c>
       <c r="C12" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2457,15 +2518,16 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2476,147 +2538,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14" t="s">
-        <v>138</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>139</v>
+      <c r="B3" t="s">
+        <v>75</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>140</v>
+      <c r="B4" t="s">
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>141</v>
+      <c r="B5" t="s">
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>142</v>
+      <c r="B6" t="s">
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>143</v>
+      <c r="B7" t="s">
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>144</v>
+      <c r="B8" t="s">
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>145</v>
+      <c r="B9" t="s">
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>146</v>
+      <c r="B10" t="s">
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>147</v>
+      <c r="B11" t="s">
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="14" t="s">
+      <c r="C14" s="18" t="s">
         <v>151</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2625,16 +2687,16 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2645,7 +2707,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2656,7 +2718,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2667,7 +2729,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2678,7 +2740,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2689,7 +2751,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2697,10 +2759,10 @@
         <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2711,7 +2773,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2722,7 +2784,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2733,7 +2795,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2744,7 +2806,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2755,7 +2817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2772,16 +2834,15 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2792,77 +2853,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>130</v>
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>150</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2873,59 +3021,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6">
-        <v>3650</v>
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2934,16 +3170,15 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2954,110 +3189,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>116</v>
+      <c r="B3" t="s">
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>102</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3068,118 +3357,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>116</v>
+      <c r="B3" t="s">
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>102</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C10" s="6"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" t="s">
-        <v>100</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="35.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3190,115 +3525,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>116</v>
+      <c r="B3" t="s">
+        <v>75</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>118</v>
+      <c r="B5" t="s">
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>91</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>119</v>
+      <c r="B7" t="s">
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>120</v>
+      <c r="B8" t="s">
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" t="s">
-        <v>100</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3309,77 +3693,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>122</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>125</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3390,77 +3861,164 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>122</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>125</v>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3471,70 +4029,147 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3545,13 +4180,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3562,7 +4197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3573,7 +4208,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3584,7 +4219,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3595,7 +4230,7 @@
         <v>-3650</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -3606,7 +4241,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -3617,7 +4252,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -3628,7 +4263,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -3639,7 +4274,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -3650,7 +4285,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -3667,16 +4302,1399 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="C10" s="6"/>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="3"/>
+      <c r="C5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3687,7 +5705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -3698,7 +5716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -3709,7 +5727,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -3720,7 +5738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -3731,7 +5749,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -3742,7 +5760,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -3753,7 +5771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -3764,7 +5782,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -3775,7 +5793,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -3786,7 +5804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -3797,7 +5815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -3808,7 +5826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -3819,7 +5837,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -3830,7 +5848,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -3841,7 +5859,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -3852,7 +5870,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -3863,7 +5881,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>85</v>
       </c>
@@ -3874,7 +5892,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -3885,7 +5903,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -3902,17 +5920,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3923,7 +5941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3940,17 +5958,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3961,7 +5979,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -3972,7 +5990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -3983,7 +6001,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3994,7 +6012,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -4011,16 +6029,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4031,7 +6049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4042,7 +6060,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4053,7 +6071,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4069,17 +6087,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4090,7 +6108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4101,7 +6119,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4112,7 +6130,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -4128,16 +6146,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4148,7 +6166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4159,7 +6177,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4176,16 +6194,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4196,7 +6214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -4204,10 +6222,10 @@
         <v>93</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4223,17 +6241,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4244,7 +6262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>85</v>
       </c>
@@ -4255,7 +6273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -4266,7 +6284,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>85</v>
       </c>
@@ -4277,7 +6295,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -4288,7 +6306,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>85</v>
       </c>
@@ -4299,7 +6317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>85</v>
       </c>
@@ -4310,7 +6328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -4321,7 +6339,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>85</v>
       </c>
@@ -4332,7 +6350,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -4343,7 +6361,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>85</v>
       </c>
@@ -4354,7 +6372,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>85</v>
       </c>
@@ -4365,7 +6383,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>85</v>
       </c>
@@ -4376,7 +6394,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>85</v>
       </c>
@@ -4387,7 +6405,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -4398,7 +6416,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -4409,7 +6427,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -4425,10 +6443,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
@@ -4439,7 +6457,7 @@
     <col min="7" max="7" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -4462,7 +6480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4485,7 +6503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -4505,7 +6523,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4525,7 +6543,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4539,1197 +6557,84 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="E6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="E7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="E8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7">
       <c r="E9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="E10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="E11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="E12" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="E13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7">
       <c r="E14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="E15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7">
       <c r="E16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="5:5">
       <c r="E17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="5:5">
       <c r="E18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="5:5">
       <c r="E19" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="5:5">
       <c r="E20" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="3"/>
-      <c r="C5" s="11"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="300" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>3700</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6">
-        <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7">
-        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -5740,14 +6645,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.28515625" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5758,7 +6663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5769,7 +6674,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5780,7 +6685,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -5797,16 +6702,129 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5817,92 +6835,847 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>117</v>
+      <c r="B5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" customWidth="1"/>
+    <col min="3" max="3" width="49.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>3700</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
       </c>
       <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>72</v>
+        <v>124</v>
+      </c>
+      <c r="C6">
+        <v>365</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6">
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -5913,13 +7686,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5930,7 +7703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -5941,7 +7714,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -5952,7 +7725,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -5963,7 +7736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -5974,7 +7747,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -5985,7 +7758,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -5996,7 +7769,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6007,7 +7780,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -6024,16 +7797,312 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7">
+        <v>460</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25.42578125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6044,7 +8113,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6055,7 +8124,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6066,7 +8135,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -6077,7 +8146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6088,7 +8157,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6099,7 +8168,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6110,7 +8179,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6121,7 +8190,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -6140,7 +8209,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A058B24C-ECE4-4154-B985-11F85C7FD554}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6149,13 +8218,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6166,7 +8235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6177,7 +8246,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -6188,7 +8257,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -6199,7 +8268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -6210,7 +8279,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15.75" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6221,7 +8290,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="15.75" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6229,10 +8298,10 @@
         <v>91</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -6240,10 +8309,10 @@
         <v>119</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -6251,7 +8320,7 @@
         <v>120</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD42D611-2A6F-4F68-BDC0-69E3F0FE2FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D997D2C3-BA81-42BC-BDC3-D9F149B23B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -46,34 +46,35 @@
     <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId31"/>
     <sheet name="Edition" sheetId="1" r:id="rId32"/>
     <sheet name="Edition_StandAlone" sheetId="9" r:id="rId33"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId34"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId35"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId36"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId37"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId38"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId39"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId40"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId41"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId42"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId43"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId44"/>
-    <sheet name="KPI" sheetId="18" r:id="rId45"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId46"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId47"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId48"/>
-    <sheet name="Grant_Creation5" sheetId="65" r:id="rId49"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId50"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId51"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId52"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId53"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId54"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId55"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId56"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId57"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId58"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId59"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId60"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId61"/>
+    <sheet name="Edition_ByAppFocusYes" sheetId="66" r:id="rId34"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
+    <sheet name="KPI" sheetId="18" r:id="rId46"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="163">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4882,6 +4883,98 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABCC2487-BBAB-4553-8D1E-751EC30790CA}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="33.21875" customWidth="1"/>
+    <col min="3" max="3" width="28.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -4996,7 +5089,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5118,7 +5211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5237,7 +5330,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5318,7 +5411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5396,97 +5489,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5554,6 +5556,97 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5789,7 +5882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5827,7 +5920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5898,7 +5991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -5956,7 +6049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6015,7 +6108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6063,7 +6156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -6110,7 +6203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6312,7 +6405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6504,120 +6597,6 @@
     <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="11.21875" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6685,6 +6664,120 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6841,7 +6934,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -6933,7 +7026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7025,7 +7118,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7117,7 +7210,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7209,7 +7302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7301,7 +7394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7392,7 +7485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7472,7 +7565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7545,97 +7638,6 @@
       </c>
       <c r="C6">
         <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7758,6 +7760,97 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
@@ -7848,7 +7941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2910DE64-7776-4AD3-A993-2E9D13CF8A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE0E177-A992-486F-89B1-7F9C92F11620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="57" activeTab="58" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="31" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -46,34 +46,35 @@
     <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId31"/>
     <sheet name="Edition" sheetId="1" r:id="rId32"/>
     <sheet name="Edition_StandAlone" sheetId="9" r:id="rId33"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId34"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId35"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId36"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId37"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId38"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId39"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId40"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId41"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId42"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId43"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId44"/>
-    <sheet name="KPI" sheetId="18" r:id="rId45"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId46"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId47"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId48"/>
-    <sheet name="Grant_Creation5" sheetId="65" r:id="rId49"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId50"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId51"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId52"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId53"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId54"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId55"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId56"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId57"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId58"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId59"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId60"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId61"/>
+    <sheet name="Edition_ByAppFocusYes" sheetId="66" r:id="rId34"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
+    <sheet name="KPI" sheetId="18" r:id="rId46"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1641" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="161">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -4883,6 +4884,98 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757E1FCF-2686-4EA9-B6EB-44427A757385}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -4997,7 +5090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5119,7 +5212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5238,7 +5331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5330,7 +5423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5419,97 +5512,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5577,6 +5579,97 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5812,7 +5905,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5850,7 +5943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5921,7 +6014,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5979,7 +6072,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6038,7 +6131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6086,7 +6179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6133,7 +6226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6335,7 +6428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6527,120 +6620,6 @@
     <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6708,6 +6687,120 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6864,7 +6957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6956,7 +7049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7048,7 +7141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7140,7 +7233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7232,7 +7325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7324,7 +7417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7415,7 +7508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7495,7 +7588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7568,97 +7661,6 @@
       </c>
       <c r="C6">
         <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7781,6 +7783,97 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7872,7 +7965,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9798C1-7F27-4D9F-A9D8-30BA3B75DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6912C6EC-DD73-44E2-9873-874C0D42316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="31" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -45,35 +45,36 @@
     <sheet name="Grant_Edition1" sheetId="30" r:id="rId30"/>
     <sheet name="Grant_Edition_Comp_Focus_No" sheetId="60" r:id="rId31"/>
     <sheet name="Edition" sheetId="1" r:id="rId32"/>
-    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId33"/>
-    <sheet name="Grant_Creation4" sheetId="36" r:id="rId34"/>
-    <sheet name="Grant_Creation3" sheetId="35" r:id="rId35"/>
-    <sheet name="Grant_Creation1" sheetId="31" r:id="rId36"/>
-    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId37"/>
-    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId38"/>
-    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId39"/>
-    <sheet name="Risk Assessment" sheetId="4" r:id="rId40"/>
-    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId41"/>
-    <sheet name="Reviewer" sheetId="6" r:id="rId42"/>
-    <sheet name="Site Visit" sheetId="5" r:id="rId43"/>
-    <sheet name="Desk Review" sheetId="7" r:id="rId44"/>
-    <sheet name="KPI" sheetId="18" r:id="rId45"/>
-    <sheet name="KPI1" sheetId="49" r:id="rId46"/>
-    <sheet name="Risk Assessment1" sheetId="29" r:id="rId47"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId48"/>
-    <sheet name="Grant_Creation5" sheetId="65" r:id="rId49"/>
-    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId50"/>
-    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId51"/>
-    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId52"/>
-    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId53"/>
-    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId54"/>
-    <sheet name="Progress Report Annually" sheetId="24" r:id="rId55"/>
-    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId56"/>
-    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId57"/>
-    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId58"/>
-    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId59"/>
-    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId60"/>
-    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId61"/>
+    <sheet name="Edition_ByAppFocusYes" sheetId="66" r:id="rId33"/>
+    <sheet name="Edition_StandAlone" sheetId="9" r:id="rId34"/>
+    <sheet name="Grant_Creation4" sheetId="36" r:id="rId35"/>
+    <sheet name="Grant_Creation3" sheetId="35" r:id="rId36"/>
+    <sheet name="Grant_Creation1" sheetId="31" r:id="rId37"/>
+    <sheet name="Payment Request Schedule" sheetId="2" r:id="rId38"/>
+    <sheet name="Progress Report Schedule" sheetId="3" r:id="rId39"/>
+    <sheet name="Progress Report Fixed Date" sheetId="28" r:id="rId40"/>
+    <sheet name="Risk Assessment" sheetId="4" r:id="rId41"/>
+    <sheet name="Risk Assessment Creation" sheetId="12" r:id="rId42"/>
+    <sheet name="Reviewer" sheetId="6" r:id="rId43"/>
+    <sheet name="Site Visit" sheetId="5" r:id="rId44"/>
+    <sheet name="Desk Review" sheetId="7" r:id="rId45"/>
+    <sheet name="KPI" sheetId="18" r:id="rId46"/>
+    <sheet name="KPI1" sheetId="49" r:id="rId47"/>
+    <sheet name="Risk Assessment1" sheetId="29" r:id="rId48"/>
+    <sheet name="Sheet1" sheetId="8" r:id="rId49"/>
+    <sheet name="Grant_Creation5" sheetId="65" r:id="rId50"/>
+    <sheet name="AdvPaymentGrandEdition" sheetId="19" r:id="rId51"/>
+    <sheet name="ProgressReport_Edition" sheetId="20" r:id="rId52"/>
+    <sheet name="ScheduledEndDateAfterStartDate" sheetId="22" r:id="rId53"/>
+    <sheet name="Progress Report Quarterly" sheetId="21" r:id="rId54"/>
+    <sheet name="Progress Report BiMonthly" sheetId="23" r:id="rId55"/>
+    <sheet name="Progress Report Annually" sheetId="24" r:id="rId56"/>
+    <sheet name="Progress Report Semi-Annually" sheetId="25" r:id="rId57"/>
+    <sheet name="Progress Report Monthly" sheetId="26" r:id="rId58"/>
+    <sheet name="Progress Report StartDate Error" sheetId="32" r:id="rId59"/>
+    <sheet name="Progress Report MoreThanOneyear" sheetId="33" r:id="rId60"/>
+    <sheet name="ProgressReportQuartelyReporting" sheetId="34" r:id="rId61"/>
+    <sheet name="Grant_Creation_Title_Error" sheetId="48" r:id="rId62"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -96,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="141">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -434,16 +435,7 @@
     <t xml:space="preserve">Automation Runtime Payment Request </t>
   </si>
   <si>
-    <t>fieldProgram__c</t>
-  </si>
-  <si>
     <t>Automation SPI3</t>
-  </si>
-  <si>
-    <t>fieldCalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldCalReportingEndDate__c</t>
   </si>
   <si>
     <t>751  August Lane1</t>
@@ -1136,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1147,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1172,7 +1164,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1249,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1260,7 +1252,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1285,7 +1277,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1343,7 +1335,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1362,7 +1354,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1373,7 +1365,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1406,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
         <v>91</v>
@@ -1476,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1487,7 +1479,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1591,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1602,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1704,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1715,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1829,7 +1821,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1840,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1998,10 +1990,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2009,10 +2001,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2179,10 +2171,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2190,10 +2182,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2348,10 +2340,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2359,10 +2351,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2516,10 +2508,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2527,10 +2519,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2831,10 +2823,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2842,10 +2834,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2999,10 +2991,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3010,10 +3002,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3167,10 +3159,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3178,10 +3170,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3335,10 +3327,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3346,10 +3338,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3503,10 +3495,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3514,10 +3506,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3671,10 +3663,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3682,10 +3674,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3839,10 +3831,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3850,10 +3842,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4007,10 +3999,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4018,10 +4010,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4175,10 +4167,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4186,10 +4178,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4244,7 +4236,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4255,7 +4247,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4457,10 +4449,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4468,10 +4460,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4625,10 +4617,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4636,10 +4628,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4684,10 +4676,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4695,7 +4687,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4706,7 +4698,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4717,7 +4709,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4730,6 +4722,97 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1CF92D-A01C-46CA-ABC1-C62A79070058}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -4765,10 +4848,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4776,7 +4859,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4787,7 +4870,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4798,7 +4881,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4809,7 +4892,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4820,7 +4903,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4831,7 +4914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -4868,7 +4951,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4879,7 +4962,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -4946,7 +5029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -4982,7 +5065,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4993,7 +5076,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5068,7 +5151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5104,7 +5187,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5115,7 +5198,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5187,7 +5270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5234,7 +5317,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5245,7 +5328,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5268,7 +5351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5315,7 +5398,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5326,7 +5409,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -5346,97 +5429,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -5504,6 +5496,97 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5739,7 +5822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5777,7 +5860,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5848,7 +5931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5887,7 +5970,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5906,7 +5989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5946,7 +6029,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5965,7 +6048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -5990,7 +6073,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>92</v>
@@ -6001,7 +6084,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6013,7 +6096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6038,10 +6121,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6049,7 +6132,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6060,7 +6143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6262,7 +6345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6454,120 +6537,6 @@
     <row r="21" spans="5:5">
       <c r="E21" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6635,6 +6604,120 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="40.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6791,7 +6874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6860,7 +6943,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6871,7 +6954,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -6883,7 +6966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -6953,7 +7036,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6964,7 +7047,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -6975,7 +7058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7045,7 +7128,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7056,7 +7139,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7067,7 +7150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7137,7 +7220,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7148,7 +7231,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7159,7 +7242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7228,7 +7311,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7239,7 +7322,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7251,7 +7334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7320,7 +7403,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7331,7 +7414,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7342,7 +7425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7400,7 +7483,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7411,7 +7494,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7422,7 +7505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7480,7 +7563,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7491,101 +7574,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>365</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7">
-        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -7640,7 +7632,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7651,7 +7643,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7708,6 +7700,97 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -7776,7 +7859,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7787,7 +7870,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7798,7 +7881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7846,7 +7929,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7857,7 +7940,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7959,7 +8042,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7970,7 +8053,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8072,7 +8155,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8083,7 +8166,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8108,7 +8191,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8119,7 +8202,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8130,7 +8213,7 @@
         <v>71</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -8189,7 +8272,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8200,7 +8283,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Creation Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E68872-20AB-410E-826F-CDF198A8431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FCACE0-E8F0-4221-B749-09DF9A96523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="46" activeTab="49" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="162">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -580,6 +580,9 @@
   </si>
   <si>
     <t>Product Sub Recipient Test Organization</t>
+  </si>
+  <si>
+    <t>New Test Org</t>
   </si>
 </sst>
 </file>
@@ -770,9 +773,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -810,7 +813,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -916,7 +919,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1058,7 +1061,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1067,10 +1070,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1126,9 +1129,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1240,10 +1243,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1353,10 +1356,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.28515625" customWidth="1"/>
+    <col min="2" max="2" width="36.54296875" customWidth="1"/>
+    <col min="3" max="3" width="39.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1466,10 +1469,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1579,11 +1582,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1694,10 +1697,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1808,9 +1811,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1922,7 +1925,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -2002,10 +2005,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2172,10 +2175,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2352,9 +2355,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2520,10 +2523,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2689,10 +2692,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2836,9 +2839,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3004,10 +3007,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3172,10 +3175,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3340,10 +3343,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3508,10 +3511,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.7265625" customWidth="1"/>
+    <col min="3" max="3" width="35.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3676,10 +3679,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3844,10 +3847,10 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4012,9 +4015,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4180,9 +4183,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4304,9 +4307,9 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4472,10 +4475,10 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="29.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4641,9 +4644,9 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4809,10 +4812,10 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7265625" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4913,9 +4916,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4978,7 +4981,7 @@
       <c r="A6" t="s">
         <v>73</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" t="s">
         <v>133</v>
       </c>
       <c r="C6">
@@ -4989,7 +4992,7 @@
       <c r="A7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" t="s">
         <v>156</v>
       </c>
       <c r="C7">
@@ -5000,7 +5003,7 @@
       <c r="A8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" t="s">
         <v>157</v>
       </c>
       <c r="C8">
@@ -5015,11 +5018,11 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5130,10 +5133,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5252,10 +5255,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5284,7 +5287,7 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" t="s">
         <v>116</v>
       </c>
       <c r="C3">
@@ -5295,7 +5298,7 @@
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" t="s">
         <v>117</v>
       </c>
       <c r="C4">
@@ -5306,7 +5309,7 @@
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" t="s">
         <v>118</v>
       </c>
       <c r="C5" t="s">
@@ -5317,18 +5320,18 @@
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" t="s">
         <v>119</v>
       </c>
       <c r="C7" t="s">
@@ -5339,7 +5342,7 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" t="s">
         <v>120</v>
       </c>
       <c r="C8" t="s">
@@ -5371,9 +5374,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5452,10 +5455,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5533,9 +5536,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5596,7 +5599,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5687,11 +5690,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5923,11 +5926,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5961,11 +5964,11 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6032,10 +6035,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6090,11 +6093,11 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6149,10 +6152,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6197,10 +6200,10 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6244,11 +6247,11 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6446,15 +6449,15 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6645,11 +6648,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6704,11 +6707,11 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6818,10 +6821,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6975,10 +6978,10 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7067,11 +7070,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" customWidth="1"/>
+    <col min="3" max="3" width="49.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7159,11 +7162,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.7265625" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7251,11 +7254,11 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.81640625" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="3" max="3" width="29.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7343,7 +7346,7 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7435,10 +7438,10 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7526,9 +7529,9 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7606,7 +7609,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7686,7 +7689,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7800,7 +7803,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7891,7 +7894,7 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7982,10 +7985,10 @@
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8096,9 +8099,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8209,7 +8212,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A058B24C-ECE4-4154-B985-11F85C7FD554}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8218,10 +8221,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8279,7 +8282,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8290,7 +8293,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Creation Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68FCACE0-E8F0-4221-B749-09DF9A96523D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD236387-393C-4822-8117-53AF05197DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1209,7 +1209,7 @@
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6912C6EC-DD73-44E2-9873-874C0D42316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0E57EE-2141-4963-ACE9-10AC82FDC473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="31" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE0E177-A992-486F-89B1-7F9C92F11620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367D2350-44AC-4F49-8689-C29D3DBC7F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="31" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="142">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -372,9 +372,6 @@
     <t>Monthly</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>Automation Permanent Internal Program</t>
   </si>
   <si>
@@ -441,24 +438,9 @@
     <t>fieldProjectTitle__c</t>
   </si>
   <si>
-    <t>fieldProjectPeriodStartDate__c</t>
-  </si>
-  <si>
-    <t>fieldProjectPeriodEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldProgram__c</t>
-  </si>
-  <si>
-    <t>fieldExternalOrganization__c</t>
-  </si>
-  <si>
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>fieldFrequency__c</t>
-  </si>
-  <si>
     <t>751  August Lane1</t>
   </si>
   <si>
@@ -474,46 +456,7 @@
     <t>Department of Health</t>
   </si>
   <si>
-    <t>fieldIsMatchRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGranteeMatch__c</t>
-  </si>
-  <si>
-    <t>fieldLaverageAllowed__c</t>
-  </si>
-  <si>
-    <t>fieldIsProgramIncomeAnticipated__c</t>
-  </si>
-  <si>
-    <t>fieldIsAdvancePermitted__c</t>
-  </si>
-  <si>
-    <t>fieldIsBuildUpFunctionality__c</t>
-  </si>
-  <si>
-    <t>fieldIsGoalsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldKPIsRequired__c</t>
-  </si>
-  <si>
-    <t>fieldAreExpensesBuildIUpLevel__c</t>
-  </si>
-  <si>
-    <t>fieldRiskAssessmentRequired__c</t>
-  </si>
-  <si>
-    <t>fieldFocusAreaRequired__c</t>
-  </si>
-  <si>
-    <t>fieldGrantType__c</t>
-  </si>
-  <si>
     <t>Directed</t>
-  </si>
-  <si>
-    <t>fieldAllocationLevel__c</t>
   </si>
   <si>
     <t>N/A</t>
@@ -1074,10 +1017,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1099,7 +1042,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1133,10 +1076,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1155,10 +1098,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1177,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1188,7 +1131,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1210,10 +1153,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1224,7 +1167,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1246,10 +1189,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="39.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1268,10 +1211,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1290,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1301,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1323,10 +1266,10 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1334,10 +1277,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1348,7 +1291,7 @@
         <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1359,10 +1302,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1381,10 +1324,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1403,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1414,7 +1357,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1436,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1447,10 +1390,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1472,11 +1415,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1495,10 +1438,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1517,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1528,7 +1471,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1550,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>69</v>
@@ -1564,7 +1507,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1575,7 +1518,7 @@
         <v>71</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1587,10 +1530,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1613,7 +1556,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1632,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1643,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1665,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1679,7 +1622,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1701,9 +1644,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1726,7 +1669,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1745,7 +1688,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1756,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1778,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -1792,7 +1735,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1815,7 +1758,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1840,7 +1783,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1870,7 +1813,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1881,7 +1824,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1895,10 +1838,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2039,10 +1982,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2050,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2065,10 +2008,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2209,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -2220,10 +2163,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2231,10 +2174,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2245,10 +2188,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2389,10 +2332,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2400,10 +2343,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2414,9 +2357,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2557,10 +2500,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2568,10 +2511,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2582,10 +2525,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2729,9 +2672,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2751,7 +2694,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>37</v>
@@ -2762,7 +2705,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -2773,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>37</v>
@@ -2784,7 +2727,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>37</v>
@@ -2795,7 +2738,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>37</v>
@@ -2806,7 +2749,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
@@ -2817,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>131</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
@@ -2828,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
         <v>37</v>
@@ -2839,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
@@ -2850,7 +2793,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -2861,7 +2804,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>37</v>
@@ -2872,10 +2815,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2883,10 +2826,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2897,10 +2840,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3040,10 +2983,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3051,10 +2994,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3065,10 +3008,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3208,10 +3151,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3219,10 +3162,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3233,10 +3176,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3376,10 +3319,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3387,10 +3330,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3401,10 +3344,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="3" max="3" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3544,10 +3487,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3555,10 +3498,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3569,10 +3512,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3712,10 +3655,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3723,10 +3666,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3737,10 +3680,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3880,10 +3823,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3891,10 +3834,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3905,9 +3848,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4048,10 +3991,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4059,10 +4002,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4073,9 +4016,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4216,10 +4159,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4227,10 +4170,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4241,9 +4184,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4263,10 +4206,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4285,7 +4228,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4296,7 +4239,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4318,7 +4261,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -4332,7 +4275,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4365,10 +4308,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4509,10 +4452,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4520,10 +4463,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4534,9 +4477,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4677,10 +4620,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4688,10 +4631,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -4702,10 +4645,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4736,10 +4679,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4747,7 +4690,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4758,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4769,7 +4712,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4784,9 +4727,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4817,10 +4760,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4828,7 +4771,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4839,7 +4782,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4850,7 +4793,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4861,7 +4804,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4872,7 +4815,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4886,11 +4829,11 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{757E1FCF-2686-4EA9-B6EB-44427A757385}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4920,10 +4863,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4931,7 +4874,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4942,7 +4885,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4953,7 +4896,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4964,7 +4907,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="C7">
         <v>2000</v>
@@ -4978,11 +4921,11 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5012,7 +4955,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5023,7 +4966,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5045,7 +4988,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5059,7 +5002,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5081,7 +5024,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -5093,10 +5036,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5126,7 +5069,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5137,7 +5080,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5159,7 +5102,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5173,7 +5116,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5195,7 +5138,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -5203,7 +5146,7 @@
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5215,10 +5158,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5248,7 +5191,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5259,7 +5202,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5281,7 +5224,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
@@ -5295,7 +5238,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -5317,12 +5260,12 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="7:7">
       <c r="G19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5334,9 +5277,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5359,7 +5302,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5378,7 +5321,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5389,7 +5332,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5426,10 +5369,10 @@
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5451,7 +5394,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5470,7 +5413,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5481,7 +5424,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5518,9 +5461,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5543,7 +5486,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5581,7 +5524,7 @@
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -5606,7 +5549,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5647,10 +5590,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -5658,7 +5601,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5672,11 +5615,11 @@
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:C20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5908,11 +5851,11 @@
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="20.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5946,11 +5889,11 @@
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6017,10 +5960,10 @@
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6042,7 +5985,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6053,7 +5996,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6075,11 +6018,11 @@
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6101,7 +6044,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6112,7 +6055,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6134,10 +6077,10 @@
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6156,10 +6099,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6167,7 +6110,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6182,10 +6125,10 @@
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F460C7BE-6B78-4C1D-8F43-EB5ECFF94C59}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6204,10 +6147,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6215,7 +6158,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6229,11 +6172,11 @@
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="61.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6431,15 +6374,15 @@
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.140625" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -6630,11 +6573,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="31.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6656,7 +6599,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6689,11 +6632,11 @@
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B06FA50-0033-457A-9572-B9C40BB74376}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" customWidth="1"/>
+    <col min="3" max="3" width="40.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6723,7 +6666,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6734,7 +6677,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6756,10 +6699,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6770,7 +6713,7 @@
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6792,7 +6735,7 @@
         <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6803,10 +6746,10 @@
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6960,10 +6903,10 @@
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -6985,7 +6928,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6996,7 +6939,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7026,7 +6969,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7037,7 +6980,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -7052,11 +6995,11 @@
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" customWidth="1"/>
-    <col min="3" max="3" width="49.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" customWidth="1"/>
+    <col min="3" max="3" width="49.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7078,7 +7021,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7089,7 +7032,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7119,7 +7062,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7130,7 +7073,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7144,11 +7087,11 @@
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7170,7 +7113,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7181,7 +7124,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7211,7 +7154,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7222,7 +7165,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7236,11 +7179,11 @@
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7262,7 +7205,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7273,7 +7216,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7303,7 +7246,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7314,7 +7257,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7328,7 +7271,7 @@
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7353,7 +7296,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7361,10 +7304,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7394,7 +7337,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7405,7 +7348,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7420,10 +7363,10 @@
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -7445,7 +7388,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7456,7 +7399,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7486,7 +7429,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7497,7 +7440,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7511,9 +7454,9 @@
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7536,7 +7479,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7566,7 +7509,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7577,7 +7520,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7591,7 +7534,7 @@
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7616,7 +7559,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7646,7 +7589,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7657,7 +7600,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7671,7 +7614,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="46" bestFit="1" customWidth="1"/>
@@ -7693,10 +7636,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7715,7 +7658,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7726,7 +7669,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7748,7 +7691,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -7762,7 +7705,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7770,7 +7713,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>72</v>
@@ -7785,7 +7728,7 @@
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -7810,7 +7753,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7851,7 +7794,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7862,7 +7805,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7876,7 +7819,7 @@
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
@@ -7901,7 +7844,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -7912,7 +7855,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -7942,7 +7885,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7953,7 +7896,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7968,10 +7911,10 @@
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{129E2C7B-C704-47A8-8150-6E03A592DEEB}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7991,10 +7934,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8013,7 +7956,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8024,7 +7967,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8046,7 +7989,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8060,7 +8003,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8082,9 +8025,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8104,10 +8047,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8126,7 +8069,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8137,7 +8080,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8159,7 +8102,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8173,7 +8116,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8195,10 +8138,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DED3A87-6AC6-43AA-AE6F-BF4F74835A6A}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8217,10 +8160,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8239,7 +8182,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8250,13 +8193,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1">
+    <row r="6" spans="1:3" ht="15" thickBot="1">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -8267,15 +8210,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1">
+    <row r="7" spans="1:3" ht="15" thickBot="1">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8283,10 +8226,10 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>70</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8294,10 +8237,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -8312,9 +8255,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8337,7 +8280,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -8356,7 +8299,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8367,7 +8310,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8389,7 +8332,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>69</v>
@@ -8403,7 +8346,7 @@
         <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367D2350-44AC-4F49-8689-C29D3DBC7F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F0A5A7-967C-43A2-A913-E125C09E3BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="32" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="59" activeTab="61" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -97,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="141">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -433,9 +433,6 @@
   </si>
   <si>
     <t xml:space="preserve">Automation Runtime Payment Request </t>
-  </si>
-  <si>
-    <t>fieldProjectTitle__c</t>
   </si>
   <si>
     <t>Automation SPI3</t>
@@ -1120,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1131,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1156,7 +1153,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1233,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1244,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1269,7 +1266,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1327,7 +1324,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1346,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1357,7 +1354,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1460,7 +1457,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4" s="9">
         <v>0</v>
@@ -1471,7 +1468,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="9">
         <v>3650</v>
@@ -1575,7 +1572,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1586,7 +1583,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1688,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1699,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>365</v>
@@ -1813,7 +1810,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>-300</v>
@@ -1824,7 +1821,7 @@
         <v>8</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>1000</v>
@@ -1982,10 +1979,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1993,10 +1990,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2163,10 +2160,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2174,10 +2171,10 @@
         <v>8</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2332,10 +2329,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2343,10 +2340,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2500,10 +2497,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2511,10 +2508,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2815,10 +2812,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2826,10 +2823,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2983,10 +2980,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2994,10 +2991,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3151,10 +3148,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3162,10 +3159,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3319,10 +3316,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3330,10 +3327,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3487,10 +3484,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3498,10 +3495,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3655,10 +3652,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3666,10 +3663,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3823,10 +3820,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -3834,10 +3831,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3991,10 +3988,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4002,10 +3999,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4159,10 +4156,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4170,10 +4167,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4228,7 +4225,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>-3650</v>
@@ -4239,7 +4236,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>900</v>
@@ -4452,10 +4449,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4463,10 +4460,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4620,10 +4617,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -4631,10 +4628,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -4679,10 +4676,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4690,7 +4687,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4701,7 +4698,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4712,7 +4709,7 @@
         <v>73</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>150</v>
@@ -4760,10 +4757,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4771,7 +4768,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4782,7 +4779,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4793,7 +4790,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4804,7 +4801,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -4815,7 +4812,7 @@
         <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -4863,10 +4860,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -4874,7 +4871,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4">
         <v>1234</v>
@@ -4885,7 +4882,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -4896,7 +4893,7 @@
         <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6">
         <v>3650</v>
@@ -4907,7 +4904,7 @@
         <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C7">
         <v>2000</v>
@@ -4955,7 +4952,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4966,7 +4963,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5069,7 +5066,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5080,7 +5077,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5191,7 +5188,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5202,7 +5199,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -5321,7 +5318,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5332,7 +5329,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5413,7 +5410,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -5424,7 +5421,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C5">
         <v>362</v>
@@ -5590,7 +5587,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>98</v>
@@ -5601,7 +5598,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -5996,7 +5993,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6055,7 +6052,7 @@
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6099,7 +6096,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>92</v>
@@ -6110,7 +6107,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6147,10 +6144,10 @@
         <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6158,7 +6155,7 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -6666,7 +6663,7 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6677,7 +6674,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4">
         <v>3650</v>
@@ -6702,7 +6699,7 @@
         <v>99</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6969,7 +6966,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -6980,7 +6977,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -7062,7 +7059,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7073,7 +7070,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>3700</v>
@@ -7154,7 +7151,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7165,7 +7162,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7246,7 +7243,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7257,7 +7254,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7337,7 +7334,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7348,7 +7345,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7429,7 +7426,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7440,7 +7437,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>365</v>
@@ -7509,7 +7506,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7520,7 +7517,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7589,7 +7586,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>-25</v>
@@ -7600,7 +7597,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6">
         <v>365</v>
@@ -7658,7 +7655,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7669,7 +7666,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -7794,7 +7791,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7805,7 +7802,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>480</v>
@@ -7885,7 +7882,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -7896,7 +7893,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C7">
         <v>460</v>
@@ -7934,7 +7931,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
         <v>104</v>
@@ -7956,7 +7953,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -7967,7 +7964,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8069,7 +8066,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8080,7 +8077,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8182,7 +8179,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8193,7 +8190,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -8218,7 +8215,7 @@
         <v>99</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -8229,7 +8226,7 @@
         <v>70</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -8240,7 +8237,7 @@
         <v>71</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -8299,7 +8296,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -8310,7 +8307,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5">
         <v>3650</v>

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Creation Org\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD236387-393C-4822-8117-53AF05197DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780BA3EB-EB6B-4A37-91A6-848C6016E514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="33" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1231,7 +1231,7 @@
         <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -5346,7 +5346,7 @@
         <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3">

--- a/src/main/resources/Award_Field_Values.xlsx
+++ b/src/main/resources/Award_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6912C6EC-DD73-44E2-9873-874C0D42316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9735B509-B010-45FE-9C20-A57B279E076C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="31" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="35" activeTab="36" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress Report Schedule_FDM" sheetId="16" r:id="rId1"/>
@@ -1025,10 +1025,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" customWidth="1"/>
+    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1084,10 +1084,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB5817C-6282-474A-8544-903751FEE950}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1197,10 +1197,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED68E7CE-CC8D-4336-AB4D-FCC4D911F847}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="39.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.54296875" customWidth="1"/>
+    <col min="3" max="3" width="39.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1310,10 +1310,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E64C7070-1AFC-4706-8E5B-A6B0F56D48B4}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1423,11 +1423,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1538,10 +1538,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1652,9 +1652,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" style="21" customWidth="1"/>
+    <col min="2" max="2" width="35.81640625" style="21" customWidth="1"/>
     <col min="3" max="3" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1766,7 +1766,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
@@ -1846,10 +1846,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2016,10 +2016,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2196,10 +2196,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2365,9 +2365,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2533,10 +2533,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E65B36E-C406-494A-B0E2-B964D6868C97}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2680,9 +2680,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0640EED7-D2C9-455A-A602-2DFF3D455D0D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2848,10 +2848,10 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C8BBCA7-84E5-468D-9593-DDDDFFC181D9}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3016,10 +3016,10 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD6EACD2-E384-4732-A671-45DCB7110B6D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3184,10 +3184,10 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA9E41-6948-44F3-A81E-083ABEFAA1FF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3352,10 +3352,10 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77BC984D-E65A-4F8B-8C91-6B719CF3E96D}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="3" max="3" width="35.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3520,10 +3520,10 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20FB1D9-E5BB-4D84-B22C-428D1F9F758E}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3688,10 +3688,10 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32AD4597-E451-4F1E-8711-FD7052A2DCDF}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -3856,9 +3856,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{234E1846-B96C-4D8F-A545-8F81DE4A8384}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4024,9 +4024,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB025003-6BB5-454C-A664-0A8352B6971A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4192,9 +4192,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
     <col min="3" max="3" width="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4305,10 +4305,10 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.81640625" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4474,9 +4474,9 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D4AB1B-6626-42AC-8E84-B372170101F0}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4642,10 +4642,10 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.81640625" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4724,9 +4724,9 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1CF92D-A01C-46CA-ABC1-C62A79070058}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4815,9 +4815,9 @@
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="2" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4917,11 +4917,11 @@
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5032,10 +5032,10 @@
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5154,10 +5154,10 @@
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5273,9 +5273,9 @@
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformat